--- a/uploads/网站信息.xlsx
+++ b/uploads/网站信息.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$H$1:$H$77</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$H$1:$H$76</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="587" uniqueCount="480">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="847" uniqueCount="695">
   <si>
     <t>分类</t>
   </si>
@@ -1040,44 +1040,13 @@
     <t>Luxury Fountain Pens &amp; Fine Writing Instruments | NibcraftPen</t>
   </si>
   <si>
-    <r>
-      <t>传世奢华钢笔与高档书写器具</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> | Nibcraft</t>
-    </r>
+    <t>传世奢华钢笔与高档书写器具 | Nibcraft</t>
   </si>
   <si>
     <t>Rediscover the art of writing. NibcraftPen offers a curated collection of luxury fountain pens and fine stationery for true connoisseurs. Find your signature piece.</t>
   </si>
   <si>
-    <r>
-      <t>重温书写艺术之美。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">NibcraftPen </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>为鉴赏家悉心甄选奢华钢笔与精致文具。寻找属于您的那支传世之作，彰显不凡品味。</t>
-    </r>
+    <t>重温书写艺术之美。NibcraftPen 为鉴赏家悉心甄选奢华钢笔与精致文具。寻找属于您的那支传世之作，彰显不凡品味。</t>
   </si>
   <si>
     <t>fountain pen</t>
@@ -1128,44 +1097,13 @@
     <t>Fine Fountain Pen Inks &amp; Archival Calligraphy Supplies | InkNestin</t>
   </si>
   <si>
-    <r>
-      <t>艺术级钢笔墨水与深邃书法色彩</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> | InkNestin</t>
-    </r>
+    <t>艺术级钢笔墨水与深邃书法色彩 | InkNestin</t>
   </si>
   <si>
     <t>Indulge in the fluid elegance of InkNestin. Explore rare, shimmering, and archival fountain pen inks curated for discerning writers and artists.</t>
   </si>
   <si>
-    <r>
-      <t>沉浸于笔尖的流动优雅。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">InkNestin </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>为挑剔的作家与艺术家，提供世所罕见的闪粉、不褪色及限定版钢笔墨水。</t>
-    </r>
+    <t>沉浸于笔尖的流动优雅。InkNestin 为挑剔的作家与艺术家，提供世所罕见的闪粉、不褪色及限定版钢笔墨水。</t>
   </si>
   <si>
     <t>fountain pen ink</t>
@@ -1222,44 +1160,13 @@
     <t>Break-Resistant Mechanical Pencil Leads &amp; Drafting Tools | LeadVersere</t>
   </si>
   <si>
-    <r>
-      <t>工业级防断自动铅笔芯与高精绘具</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> | LeadVersere</t>
-    </r>
+    <t>工业级防断自动铅笔芯与高精绘具 | LeadVersere</t>
   </si>
   <si>
     <t>Engineered for absolute precision. LeadVersere provides high-polymer, break-resistant pencil lead refills (0.5/0.7/HB) built for rigorous drafting and design.</t>
   </si>
   <si>
-    <r>
-      <t>为绝对的精准而工程化。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">LeadVersere </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>专为高强度绘图与结构设计，提供高聚物防断裂自动铅笔芯及专业工程书写工具。</t>
-    </r>
+    <t>为绝对的精准而工程化。LeadVersere 专为高强度绘图与结构设计，提供高聚物防断裂自动铅笔芯及专业工程书写工具。</t>
   </si>
   <si>
     <t>mechanical pencil lead</t>
@@ -1286,44 +1193,13 @@
     <t>Luxury Cardstock &amp; Premium Textured Craft Paper | PaperPackh</t>
   </si>
   <si>
-    <r>
-      <t>奢华艺术卡纸与触觉系手工纸艺</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> | PaperPackh</t>
-    </r>
+    <t>奢华艺术卡纸与触觉系手工纸艺 | PaperPackh</t>
   </si>
   <si>
     <t>Touch the texture of creativity. PaperPackh crafts premium cardstock and textured paper packs for bespoke invitations, memories, and timeless paper arts.</t>
   </si>
   <si>
-    <r>
-      <t>指尖轻触，便是创意的质感。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">PaperPackh </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>为高端定制邀请函及手作艺术，提供高磅数卡纸与肌理触感纸艺套装。</t>
-    </r>
+    <t>指尖轻触，便是创意的质感。PaperPackh 为高端定制邀请函及手作艺术，提供高磅数卡纸与肌理触感纸艺套装。</t>
   </si>
   <si>
     <t>paper packs</t>
@@ -1594,6 +1470,651 @@
   </si>
   <si>
     <t>laser measuring tools, survey equipment, digital tape measure, precision measuring tools, construction layout tools, woodworking measuring tools</t>
+  </si>
+  <si>
+    <t>擦手巾</t>
+  </si>
+  <si>
+    <t>Hand Towels</t>
+  </si>
+  <si>
+    <t>54991,54993,54995,54974,54976,54978,55048,55050,55052</t>
+  </si>
+  <si>
+    <t>4650 Nelson St, Fremont, CA 94538</t>
+  </si>
+  <si>
+    <t>coastallooms.com</t>
+  </si>
+  <si>
+    <t>Bring Resort Comfort Into Your Bathroom</t>
+  </si>
+  <si>
+    <t>将度假酒店般的舒适带回家</t>
+  </si>
+  <si>
+    <t>Premium hand towels, bath linens, spa-inspired textiles, guest bathroom essentials, and luxury home accessories inspired by coastal living and warm-weather lifestyles.</t>
+  </si>
+  <si>
+    <t>提供高端手巾、浴室织物、SPA风格家纺及客用浴室用品，灵感来自美国海岸度假生活方式。</t>
+  </si>
+  <si>
+    <t>hand towels</t>
+  </si>
+  <si>
+    <t>luxury hand towels, bathroom hand towels, cotton guest towels, spa bath linens, decorative hand towels, quick dry hand towels</t>
+  </si>
+  <si>
+    <t>园艺球茎</t>
+  </si>
+  <si>
+    <t>Garden Bulbs</t>
+  </si>
+  <si>
+    <t>55003,55005,55007,55001,55009,55011,55022,55024,55026</t>
+  </si>
+  <si>
+    <t>1185 E 22nd Ave, Columbus, OH 43211</t>
+  </si>
+  <si>
+    <t>prairbloom.com</t>
+  </si>
+  <si>
+    <t>Bring Your Midwest Garden to Life with Seasonal Bulbs</t>
+  </si>
+  <si>
+    <t>用四季花卉打造美式庭院花园</t>
+  </si>
+  <si>
+    <t>From tulips that survive snowy winters to vibrant spring daffodils, find bulbs selected for Midwest climates, backyard landscapes, and neighborhood curb appeal.</t>
+  </si>
+  <si>
+    <t>提供适合美国中西部气候的郁金香、水仙等球根花卉，帮助打造具有社区观赏价值的美式庭院。</t>
+  </si>
+  <si>
+    <t>garden bulbs</t>
+  </si>
+  <si>
+    <t>tulip bulbs for zone 5, perennial flower bulbs, spring blooming bulbs, backyard flower garden</t>
+  </si>
+  <si>
+    <t>西式厨刀</t>
+  </si>
+  <si>
+    <t>Western Kitchen Knives</t>
+  </si>
+  <si>
+    <t>55029,55031,55034,55042,55044,55046,55062,55063,55064</t>
+  </si>
+  <si>
+    <t>1520 Beverly St, Odessa, TX 79761</t>
+  </si>
+  <si>
+    <t>lonestarblad.com</t>
+  </si>
+  <si>
+    <t>Built for BBQ, Brisket and Serious Cooking</t>
+  </si>
+  <si>
+    <t>为烧烤、牛胸肉和专业烹饪打造</t>
+  </si>
+  <si>
+    <t>Premium western-style kitchen knives designed for brisket trimming, outdoor cooking, hunting camps, ranch kitchens, and Texas barbecue enthusiasts.</t>
+  </si>
+  <si>
+    <t>专为德州烧烤、牛肉处理、户外烹饪和牧场厨房设计的西式厨刀。</t>
+  </si>
+  <si>
+    <t>western kitchen knives</t>
+  </si>
+  <si>
+    <t>brisket knife, BBQ slicing knife, chef knife for meat, texas kitchen knife</t>
+  </si>
+  <si>
+    <t>季节性商品|||圣诞节|||圣诞树挂饰</t>
+  </si>
+  <si>
+    <t>Seasonal|||Christmas|||Baubles Tree Decorations</t>
+  </si>
+  <si>
+    <t>54998,55000,55013,54983,54985,54987,54972,54980,54981</t>
+  </si>
+  <si>
+    <t>503 Quincy St, Brooklyn, NY 11221</t>
+  </si>
+  <si>
+    <t>ahollyhearth.com</t>
+  </si>
+  <si>
+    <t>Create a Christmas Tree Worth Gathering Around</t>
+  </si>
+  <si>
+    <t>打造全家围绕的圣诞树</t>
+  </si>
+  <si>
+    <t>Curated ornaments, heirloom baubles, tree toppers, and seasonal décor inspired by classic American Christmas traditions and family celebrations.</t>
+  </si>
+  <si>
+    <t>提供经典美式圣诞传统风格的树饰、彩球和节日装饰品。</t>
+  </si>
+  <si>
+    <t>christmas ornaments</t>
+  </si>
+  <si>
+    <t>christmas tree baubles, vintage ornaments, family christmas decor, holiday tree decorations</t>
+  </si>
+  <si>
+    <t>园艺|||户外|||养蜂设备</t>
+  </si>
+  <si>
+    <t>Gardening|||Outdoors|||Bee Keeping Equipment</t>
+  </si>
+  <si>
+    <t>55065,55066,55067,55020,55028,55036,55061,55068,55069</t>
+  </si>
+  <si>
+    <t>1000 Storey Ave, Midland, TX 79701</t>
+  </si>
+  <si>
+    <t>goldenhivecobe.com</t>
+  </si>
+  <si>
+    <t>From Backyard Hives to Honey Harvests</t>
+  </si>
+  <si>
+    <t>从后院蜂箱到蜂蜜收获</t>
+  </si>
+  <si>
+    <t>Equipment for hobby beekeepers, small farms, and homesteaders raising healthy colonies and producing local honey throughout warm southern climates.</t>
+  </si>
+  <si>
+    <t>面向家庭养蜂者和小型农场的养蜂设备，适合美国南部地区蜂蜜生产。</t>
+  </si>
+  <si>
+    <t>beekeeping equipment</t>
+  </si>
+  <si>
+    <t>bee hive kits, honey harvesting tools, beginner beekeeping, apiary supplies</t>
+  </si>
+  <si>
+    <t>洗碗布套装</t>
+  </si>
+  <si>
+    <t>Dishcloth Set</t>
+  </si>
+  <si>
+    <t>54989,55015,55018,54967,54969,55038,55059,55070,55071</t>
+  </si>
+  <si>
+    <t>1070 Langlade Ave, Green Bay, WI 54304</t>
+  </si>
+  <si>
+    <t>harvestlinen.com</t>
+  </si>
+  <si>
+    <t>Everyday Kitchen Linens for Busy American Homes</t>
+  </si>
+  <si>
+    <t>为美国家庭打造的高品质厨房布艺</t>
+  </si>
+  <si>
+    <t>Soft, absorbent dishcloths, kitchen towels, drying mats, table linens, and farmhouse-inspired essentials designed for daily cooking, family meals, and modern home living.</t>
+  </si>
+  <si>
+    <t>提供吸水洗碗布、厨房毛巾、沥水垫及餐桌布艺用品，融合美式农舍风格与现代家庭厨房需求。</t>
+  </si>
+  <si>
+    <t>dishcloth set</t>
+  </si>
+  <si>
+    <t>cotton dishcloth set, kitchen cleaning cloths, farmhouse kitchen towels, reusable dish cloths, absorbent dishcloths, kitchen linen sets</t>
+  </si>
+  <si>
+    <t>匹克球拍</t>
+  </si>
+  <si>
+    <t>Pickleball Paddle</t>
+  </si>
+  <si>
+    <t>体育用品</t>
+  </si>
+  <si>
+    <t>54876,54877,54881,54882,54885,54886,54890,54891,54893</t>
+  </si>
+  <si>
+    <t>816 Pinedale Ave, Orlando, FL 32808</t>
+  </si>
+  <si>
+    <t>coupicpaddle.com</t>
+  </si>
+  <si>
+    <t>Play Faster. Hit Smarter. Win More.</t>
+  </si>
+  <si>
+    <t>更快、更准、更强</t>
+  </si>
+  <si>
+    <t>Performance paddles, court gear, and training accessories designed for recreational leagues and competitive pickleball players.</t>
+  </si>
+  <si>
+    <t>为休闲联赛和竞技玩家打造的匹克球装备平台。</t>
+  </si>
+  <si>
+    <t>pickleball paddle</t>
+  </si>
+  <si>
+    <t>carbon pickleball paddle, pickleball gear, pickleball accessories, tournament paddle</t>
+  </si>
+  <si>
+    <t>骑行配件</t>
+  </si>
+  <si>
+    <t>Cycling Accessories</t>
+  </si>
+  <si>
+    <t>54874,54875,54896,54897,54900,54901,54888,54889,54904</t>
+  </si>
+  <si>
+    <t>2429 N Downing St, Denver, CO 80205</t>
+  </si>
+  <si>
+    <t>alpinpedal.com</t>
+  </si>
+  <si>
+    <t>Built for Long Climbs and Epic Descents</t>
+  </si>
+  <si>
+    <t>为爬坡与下坡而生</t>
+  </si>
+  <si>
+    <t>Bike accessories chosen for mountain trails, gravel roads, endurance rides, and outdoor adventures across the Rockies.</t>
+  </si>
+  <si>
+    <t>专为山地骑行、碎石路骑行及长途探险设计。</t>
+  </si>
+  <si>
+    <t>cycling accessories</t>
+  </si>
+  <si>
+    <t>bikepacking gear, cycling accessories, MTB equipment, cycling lights</t>
+  </si>
+  <si>
+    <t>哑铃</t>
+  </si>
+  <si>
+    <t>Dumbbells</t>
+  </si>
+  <si>
+    <t>54905,54907,54908,54911,54912,54899,54902,54914,54915</t>
+  </si>
+  <si>
+    <t>1423 Maple St, Lakeland, FL 33810</t>
+  </si>
+  <si>
+    <t>ironhomelab.com</t>
+  </si>
+  <si>
+    <t>Stronger at Home Starts Here</t>
+  </si>
+  <si>
+    <t>在家练出更强自己</t>
+  </si>
+  <si>
+    <t>Adjustable dumbbells, workout equipment, and strength systems designed for busy professionals building home gyms.</t>
+  </si>
+  <si>
+    <t>面向家庭健身和力量训练用户的专业器械平台。</t>
+  </si>
+  <si>
+    <t>dumbbells</t>
+  </si>
+  <si>
+    <t>adjustable dumbbells, home gym equipment, strength training gear, workout weights</t>
+  </si>
+  <si>
+    <t>水壶</t>
+  </si>
+  <si>
+    <t>Water Bottles</t>
+  </si>
+  <si>
+    <t>54884,54887,54880,54883,54873,54878,54918,54919,54920</t>
+  </si>
+  <si>
+    <t>6500 Xavier Ct, Arvada, CO 80003</t>
+  </si>
+  <si>
+    <t>summitaflow.com</t>
+  </si>
+  <si>
+    <t>Stay Hydrated Wherever the Trail Leads</t>
+  </si>
+  <si>
+    <t>无论走到哪里都保持补水</t>
+  </si>
+  <si>
+    <t>Durable insulated bottles and hydration gear for hiking, camping, fitness training, and life on the move.</t>
+  </si>
+  <si>
+    <t>面向徒步、露营和运动人群的补水装备平台。</t>
+  </si>
+  <si>
+    <t>water bottles</t>
+  </si>
+  <si>
+    <t>insulated water bottle, hiking water bottle, stainless steel bottle, sports bottle</t>
+  </si>
+  <si>
+    <t>网球拍</t>
+  </si>
+  <si>
+    <t>Tennis Racquets</t>
+  </si>
+  <si>
+    <t>54879,54892,54871,54872,54869,54870,54868,54894,54910</t>
+  </si>
+  <si>
+    <t>732 Fairlane Ave, Santa Clara, CA 95051</t>
+  </si>
+  <si>
+    <t>baselineten.com</t>
+  </si>
+  <si>
+    <t>Every Point Starts with the Right Racquet</t>
+  </si>
+  <si>
+    <t>每一分都始于正确的球拍</t>
+  </si>
+  <si>
+    <t>Racquets, strings, and training gear selected for club players, juniors, and tournament competitors.</t>
+  </si>
+  <si>
+    <t>面向俱乐部球员和赛事选手的专业网球装备。</t>
+  </si>
+  <si>
+    <t>tennis racquet</t>
+  </si>
+  <si>
+    <t>best tennis racquet, tennis strings, tennis training equipment, performance racquet</t>
+  </si>
+  <si>
+    <t>滑雪镜</t>
+  </si>
+  <si>
+    <t>Ski Goggles</t>
+  </si>
+  <si>
+    <t>54916,54917,54909,54913,54906,54921,54895,54898,54867</t>
+  </si>
+  <si>
+    <t>1085 Jasmine St, Denver, CO 80220</t>
+  </si>
+  <si>
+    <t>peakvesion.com</t>
+  </si>
+  <si>
+    <t>See Every Line on the Mountain</t>
+  </si>
+  <si>
+    <t>看清雪道上的每一条线路</t>
+  </si>
+  <si>
+    <t>Premium goggles engineered for changing mountain weather, powder days, and high-altitude winter adventures.</t>
+  </si>
+  <si>
+    <t>专为落基山脉复杂雪况和高海拔环境设计。</t>
+  </si>
+  <si>
+    <t>ski goggles</t>
+  </si>
+  <si>
+    <t>anti fog ski goggles, snow goggles, ski accessories, winter sports gear</t>
+  </si>
+  <si>
+    <t>板球棒</t>
+  </si>
+  <si>
+    <t>Cricket Bat</t>
+  </si>
+  <si>
+    <t>54866,54903,54922</t>
+  </si>
+  <si>
+    <t>1620 West End Pl, Elizabeth, NJ 07202</t>
+  </si>
+  <si>
+    <t>willowleague.com</t>
+  </si>
+  <si>
+    <t>Gear for the New Generation of American Cricket</t>
+  </si>
+  <si>
+    <t>为美国新一代板球玩家打造</t>
+  </si>
+  <si>
+    <t>Cricket bats, protection, and training equipment supporting the rapidly growing cricket communities across the U.S.</t>
+  </si>
+  <si>
+    <t>服务美国快速增长的板球社群。</t>
+  </si>
+  <si>
+    <t>cricket bat</t>
+  </si>
+  <si>
+    <t>english willow bat, cricket gear, cricket equipment, cricket training kit</t>
+  </si>
+  <si>
+    <t>露营灯</t>
+  </si>
+  <si>
+    <t>Camping Lights</t>
+  </si>
+  <si>
+    <t>3133 E 133rd Ave, Thornton, CO 80241</t>
+  </si>
+  <si>
+    <t>trailisbeacon.com</t>
+  </si>
+  <si>
+    <t>Light Up Every Camp After Sunset</t>
+  </si>
+  <si>
+    <t>点亮每一次露营之夜</t>
+  </si>
+  <si>
+    <t>Reliable lighting systems for campgrounds, overlanding trips, hunting camps, and off-grid outdoor adventures.</t>
+  </si>
+  <si>
+    <t>面向露营、自驾穿越和户外探险用户。</t>
+  </si>
+  <si>
+    <t>camping lights</t>
+  </si>
+  <si>
+    <t>camping lantern, rechargeable camp light, outdoor lighting gear, overlanding lights</t>
+  </si>
+  <si>
+    <t>高尔夫球</t>
+  </si>
+  <si>
+    <t>Golf Balls</t>
+  </si>
+  <si>
+    <t>329 W Encanto Blvd, Phoenix, AZ 85003</t>
+  </si>
+  <si>
+    <t>flightpagolf.com</t>
+  </si>
+  <si>
+    <t>Longer Drives Start with Better Balls</t>
+  </si>
+  <si>
+    <t>更远开球从更好的球开始</t>
+  </si>
+  <si>
+    <t>Golf balls engineered for distance, control, and consistency on courses throughout America's golf capitals.</t>
+  </si>
+  <si>
+    <t>为美国高尔夫热门地区球场环境优化的高性能高尔夫球。</t>
+  </si>
+  <si>
+    <t>golf balls</t>
+  </si>
+  <si>
+    <t>premium golf balls, distance golf balls, golf accessories, tour golf balls</t>
+  </si>
+  <si>
+    <t>高尔夫球杆</t>
+  </si>
+  <si>
+    <t>Golf Clubs</t>
+  </si>
+  <si>
+    <t>2113 Encanto Dr SE, Phoenix, AZ 85007</t>
+  </si>
+  <si>
+    <t>fairwaycrafted.com</t>
+  </si>
+  <si>
+    <t>Clubs Matched to Your Swing</t>
+  </si>
+  <si>
+    <t>专属于你的挥杆球杆</t>
+  </si>
+  <si>
+    <t>Custom-fit drivers, irons, wedges, and premium golf equipment tailored for players seeking lower scores and better consistency.</t>
+  </si>
+  <si>
+    <t>面向追求成绩提升的高尔夫玩家提供定制化球杆方案。</t>
+  </si>
+  <si>
+    <t>golf clubs</t>
+  </si>
+  <si>
+    <t>golf driver, custom golf clubs, golf iron set, golf fitting equipment</t>
+  </si>
+  <si>
+    <t>种植容器|||花盆与种植箱</t>
+  </si>
+  <si>
+    <t>Planters|||Pots and Containers</t>
+  </si>
+  <si>
+    <t>55040,55053,55055,55057,55072</t>
+  </si>
+  <si>
+    <t>2720 22nd Ave, Oakland, CA 94606</t>
+  </si>
+  <si>
+    <t>terraverdhome.com</t>
+  </si>
+  <si>
+    <t>Elevate Patios, Decks and Garden Spaces</t>
+  </si>
+  <si>
+    <t>打造加州风格庭院生活</t>
+  </si>
+  <si>
+    <t>Modern planters and outdoor containers inspired by California landscapes, drought-friendly gardening, and stylish outdoor living spaces.</t>
+  </si>
+  <si>
+    <t>结合加州庭院文化与节水园艺理念设计的花盆与户外种植容器。</t>
+  </si>
+  <si>
+    <t>garden planters</t>
+  </si>
+  <si>
+    <t>patio planters, large outdoor pots, container gardening, drought tolerant planters</t>
+  </si>
+  <si>
+    <t>马克杯</t>
+  </si>
+  <si>
+    <t>Mug</t>
+  </si>
+  <si>
+    <t>36557 31st Ave S, Federal Way, WA 98003</t>
+  </si>
+  <si>
+    <t>northroastmug.com</t>
+  </si>
+  <si>
+    <t>Coffee Starts Here</t>
+  </si>
+  <si>
+    <t>咖啡生活从这里开始</t>
+  </si>
+  <si>
+    <t>Crafted mugs and drinkware designed for specialty coffee lovers, morning rituals, remote workers, and Pacific Northwest café culture.</t>
+  </si>
+  <si>
+    <t>面向精品咖啡爱好者、远程办公人群和西北海岸咖啡文化用户。</t>
+  </si>
+  <si>
+    <t>coffee mug</t>
+  </si>
+  <si>
+    <t>ceramic coffee mug, artisan mugs, latte mug, coffee lover gifts</t>
+  </si>
+  <si>
+    <t>磨刀工具</t>
+  </si>
+  <si>
+    <t>Sharpening Supplies</t>
+  </si>
+  <si>
+    <t>715 S Washington St, Casper, WY 82601</t>
+  </si>
+  <si>
+    <t>edgefronti.com</t>
+  </si>
+  <si>
+    <t>Keep Every Edge Ready for the Next Adventure</t>
+  </si>
+  <si>
+    <t>让每一把刀保持最佳状态</t>
+  </si>
+  <si>
+    <t>Sharpening stones, field sharpeners, and maintenance tools trusted by hunters, outdoorsmen, ranchers, and knife enthusiasts.</t>
+  </si>
+  <si>
+    <t>为猎人、户外玩家及刀具爱好者提供专业磨刀与保养工具。</t>
+  </si>
+  <si>
+    <t>sharpening supplies</t>
+  </si>
+  <si>
+    <t>whetstone kit, hunting knife sharpener, sharpening stone set, blade maintenance</t>
+  </si>
+  <si>
+    <t>清洁用品|||刷子|||扫帚</t>
+  </si>
+  <si>
+    <t>Cleaning Products|||Brushes|||Brooms</t>
+  </si>
+  <si>
+    <t>2805 Ione St, Sacramento, CA 95821</t>
+  </si>
+  <si>
+    <t>cleaninshift.com</t>
+  </si>
+  <si>
+    <t>Cleaning Tools That Work as Hard as You Do</t>
+  </si>
+  <si>
+    <t>与您一样勤奋工作的清洁工具</t>
+  </si>
+  <si>
+    <t>Commercial-grade brushes, brooms, and cleaning essentials built for busy households, facilities, restaurants, and maintenance crews.</t>
+  </si>
+  <si>
+    <t>面向家庭、商业场所和物业维护团队的专业清洁用品。</t>
+  </si>
+  <si>
+    <t>cleaning supplies</t>
+  </si>
+  <si>
+    <t>commercial cleaning tools, floor brooms, janitorial supplies, cleaning brushes</t>
   </si>
 </sst>
 </file>
@@ -1606,7 +2127,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1804,18 +2325,6 @@
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
     </font>
   </fonts>
   <fills count="34">
@@ -2289,7 +2798,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2317,41 +2826,41 @@
     <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -2384,13 +2893,25 @@
         </ext>
       </extLst>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3044,10 +3565,6 @@
 <ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{00000000-0000-0000-0000-000000000000}" r:id="rId1" ax:persistence="persistStreamInit"/>
 </file>
 
-<file path=xl/activeX/activeX95.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{00000000-0000-0000-0000-000000000000}" r:id="rId1" ax:persistence="persistStreamInit"/>
-</file>
-
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -3078,7 +3595,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9697720" y="19939000"/>
+              <a:off x="10370820" y="20881975"/>
               <a:ext cx="1143635" cy="180975"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -3119,7 +3636,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9697720" y="19939000"/>
+              <a:off x="10370820" y="20881975"/>
               <a:ext cx="1143635" cy="180975"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -3160,7 +3677,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9697720" y="19939000"/>
+              <a:off x="10370820" y="20881975"/>
               <a:ext cx="1143635" cy="180975"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -3201,7 +3718,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9697720" y="19939000"/>
+              <a:off x="10370820" y="20881975"/>
               <a:ext cx="1143635" cy="180975"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -3242,7 +3759,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9697720" y="19939000"/>
+              <a:off x="10370820" y="20881975"/>
               <a:ext cx="1143635" cy="180975"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -3283,7 +3800,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9697720" y="19939000"/>
+              <a:off x="10370820" y="20881975"/>
               <a:ext cx="1143635" cy="180975"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -3324,7 +3841,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9697720" y="19939000"/>
+              <a:off x="10370820" y="20881975"/>
               <a:ext cx="1143635" cy="180975"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -3365,7 +3882,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9697720" y="19939000"/>
+              <a:off x="10370820" y="20881975"/>
               <a:ext cx="1143635" cy="180975"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -3406,7 +3923,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9697720" y="19939000"/>
+              <a:off x="10370820" y="20881975"/>
               <a:ext cx="1143635" cy="180975"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -3447,7 +3964,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9697720" y="19939000"/>
+              <a:off x="10370820" y="20881975"/>
               <a:ext cx="1143635" cy="180975"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -3488,7 +4005,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9697720" y="19939000"/>
+              <a:off x="10370820" y="20881975"/>
               <a:ext cx="1143635" cy="180975"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -3529,7 +4046,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9697720" y="19939000"/>
+              <a:off x="10370820" y="20881975"/>
               <a:ext cx="1143635" cy="180975"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -3570,7 +4087,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9697720" y="19939000"/>
+              <a:off x="10370820" y="20881975"/>
               <a:ext cx="1143635" cy="180975"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -3611,7 +4128,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9697720" y="19939000"/>
+              <a:off x="10370820" y="20881975"/>
               <a:ext cx="1143635" cy="180975"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -3652,7 +4169,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9697720" y="19939000"/>
+              <a:off x="10370820" y="20881975"/>
               <a:ext cx="1143635" cy="180975"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -3693,7 +4210,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9697720" y="19939000"/>
+              <a:off x="10370820" y="20881975"/>
               <a:ext cx="1143635" cy="180975"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -3734,7 +4251,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9697720" y="19939000"/>
+              <a:off x="10370820" y="20881975"/>
               <a:ext cx="1143635" cy="180975"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -3775,7 +4292,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9697720" y="19939000"/>
+              <a:off x="10370820" y="20881975"/>
               <a:ext cx="1143635" cy="180975"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -3816,7 +4333,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9697720" y="19939000"/>
+              <a:off x="10370820" y="20881975"/>
               <a:ext cx="1143635" cy="180975"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -3857,7 +4374,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9697720" y="19939000"/>
+              <a:off x="10370820" y="20881975"/>
               <a:ext cx="1143635" cy="180975"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -3898,7 +4415,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9697720" y="19939000"/>
+              <a:off x="10370820" y="20881975"/>
               <a:ext cx="1143635" cy="180975"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -3939,7 +4456,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9697720" y="19939000"/>
+              <a:off x="10370820" y="20881975"/>
               <a:ext cx="1143635" cy="180975"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -3980,7 +4497,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9697720" y="19939000"/>
+              <a:off x="10370820" y="20881975"/>
               <a:ext cx="1143635" cy="180975"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -4021,7 +4538,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9697720" y="19939000"/>
+              <a:off x="10370820" y="20881975"/>
               <a:ext cx="1143635" cy="180975"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -4062,7 +4579,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9697720" y="19939000"/>
+              <a:off x="10370820" y="20881975"/>
               <a:ext cx="1143635" cy="180975"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -4103,7 +4620,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9697720" y="19939000"/>
+              <a:off x="10370820" y="20881975"/>
               <a:ext cx="1143635" cy="180975"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -4144,7 +4661,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9697720" y="19939000"/>
+              <a:off x="10370820" y="20881975"/>
               <a:ext cx="1143635" cy="180975"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -4185,7 +4702,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9697720" y="19939000"/>
+              <a:off x="10370820" y="20881975"/>
               <a:ext cx="1143635" cy="180975"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -4226,7 +4743,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9697720" y="19939000"/>
+              <a:off x="10370820" y="20881975"/>
               <a:ext cx="1143635" cy="180975"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -4267,7 +4784,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9697720" y="19939000"/>
+              <a:off x="10370820" y="20881975"/>
               <a:ext cx="1143635" cy="180975"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -4308,7 +4825,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9697720" y="19939000"/>
+              <a:off x="10370820" y="20881975"/>
               <a:ext cx="1143635" cy="180975"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -4349,7 +4866,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9697720" y="19939000"/>
+              <a:off x="10370820" y="20881975"/>
               <a:ext cx="1143635" cy="180975"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -4390,7 +4907,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9697720" y="19939000"/>
+              <a:off x="10370820" y="20881975"/>
               <a:ext cx="1143635" cy="180975"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -4431,7 +4948,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9697720" y="19939000"/>
+              <a:off x="10370820" y="20881975"/>
               <a:ext cx="1143635" cy="180975"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -4472,7 +4989,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9697720" y="19939000"/>
+              <a:off x="10370820" y="20881975"/>
               <a:ext cx="1143635" cy="180975"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -4513,7 +5030,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9697720" y="19939000"/>
+              <a:off x="10370820" y="20881975"/>
               <a:ext cx="1143635" cy="180975"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -4554,7 +5071,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9697720" y="19939000"/>
+              <a:off x="10370820" y="20881975"/>
               <a:ext cx="1143635" cy="180975"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -4595,7 +5112,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9697720" y="19939000"/>
+              <a:off x="10370820" y="20881975"/>
               <a:ext cx="1143635" cy="180975"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -4636,7 +5153,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9697720" y="19939000"/>
+              <a:off x="10370820" y="20881975"/>
               <a:ext cx="1143635" cy="180975"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -4677,7 +5194,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9697720" y="19939000"/>
+              <a:off x="10370820" y="20881975"/>
               <a:ext cx="1143635" cy="180975"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -4718,7 +5235,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9697720" y="19939000"/>
+              <a:off x="10370820" y="20881975"/>
               <a:ext cx="1143635" cy="180975"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -4759,7 +5276,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9697720" y="19939000"/>
+              <a:off x="10370820" y="20881975"/>
               <a:ext cx="1143635" cy="180975"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -4800,7 +5317,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9697720" y="19939000"/>
+              <a:off x="10370820" y="20881975"/>
               <a:ext cx="1143635" cy="180975"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -4841,7 +5358,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9697720" y="19939000"/>
+              <a:off x="10370820" y="20881975"/>
               <a:ext cx="1143635" cy="180975"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -4882,7 +5399,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9697720" y="19939000"/>
+              <a:off x="10370820" y="20881975"/>
               <a:ext cx="1143635" cy="180975"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -4923,7 +5440,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9697720" y="19939000"/>
+              <a:off x="10370820" y="20881975"/>
               <a:ext cx="1143635" cy="180975"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -4964,7 +5481,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9697720" y="19939000"/>
+              <a:off x="10370820" y="20881975"/>
               <a:ext cx="1143635" cy="180975"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -5005,7 +5522,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9697720" y="19939000"/>
+              <a:off x="10370820" y="20881975"/>
               <a:ext cx="1143635" cy="180975"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -5046,7 +5563,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9697720" y="19939000"/>
+              <a:off x="10370820" y="20881975"/>
               <a:ext cx="1143635" cy="180975"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -5087,7 +5604,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9697720" y="19939000"/>
+              <a:off x="10370820" y="20881975"/>
               <a:ext cx="1143635" cy="180975"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -5128,7 +5645,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9697720" y="19939000"/>
+              <a:off x="10370820" y="20881975"/>
               <a:ext cx="1143635" cy="180975"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -5169,7 +5686,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9697720" y="19939000"/>
+              <a:off x="10370820" y="20881975"/>
               <a:ext cx="1143635" cy="180975"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -5210,7 +5727,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9697720" y="19939000"/>
+              <a:off x="10370820" y="20881975"/>
               <a:ext cx="1143635" cy="180975"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -5251,7 +5768,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9697720" y="19939000"/>
+              <a:off x="10370820" y="20881975"/>
               <a:ext cx="1143635" cy="180975"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -5292,7 +5809,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9697720" y="19939000"/>
+              <a:off x="10370820" y="20881975"/>
               <a:ext cx="1143635" cy="180975"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -5333,7 +5850,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9697720" y="19939000"/>
+              <a:off x="10370820" y="20881975"/>
               <a:ext cx="1143635" cy="180975"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -5374,7 +5891,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9697720" y="19939000"/>
+              <a:off x="10370820" y="20881975"/>
               <a:ext cx="1143635" cy="180975"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -5415,7 +5932,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9697720" y="19939000"/>
+              <a:off x="10370820" y="20881975"/>
               <a:ext cx="1143635" cy="180975"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -5456,7 +5973,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9697720" y="19939000"/>
+              <a:off x="10370820" y="20881975"/>
               <a:ext cx="1143635" cy="180975"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -5497,7 +6014,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9697720" y="20634325"/>
+              <a:off x="10370820" y="21688425"/>
               <a:ext cx="1143635" cy="180975"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -5538,7 +6055,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9697720" y="21329650"/>
+              <a:off x="10370820" y="22494875"/>
               <a:ext cx="1143635" cy="180975"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -5579,7 +6096,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9697720" y="22024975"/>
+              <a:off x="10370820" y="23301325"/>
               <a:ext cx="1143635" cy="180975"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -5620,7 +6137,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9697720" y="22710775"/>
+              <a:off x="10370820" y="24107775"/>
               <a:ext cx="1143635" cy="180975"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -5661,7 +6178,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9697720" y="23396575"/>
+              <a:off x="10370820" y="24914225"/>
               <a:ext cx="1143635" cy="180975"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -5702,7 +6219,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9697720" y="24425275"/>
+              <a:off x="10370820" y="26139775"/>
               <a:ext cx="1143635" cy="180975"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -5743,7 +6260,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9697720" y="25453975"/>
+              <a:off x="10370820" y="27365325"/>
               <a:ext cx="1143635" cy="180975"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -5784,7 +6301,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9697720" y="26482675"/>
+              <a:off x="10370820" y="28590875"/>
               <a:ext cx="1143635" cy="180975"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -5825,7 +6342,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9697720" y="27511375"/>
+              <a:off x="10370820" y="29816425"/>
               <a:ext cx="1143635" cy="180975"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -5866,7 +6383,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9697720" y="28378150"/>
+              <a:off x="10370820" y="30832425"/>
               <a:ext cx="1143635" cy="180975"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -5907,7 +6424,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9697720" y="29244925"/>
+              <a:off x="10370820" y="32057975"/>
               <a:ext cx="1143635" cy="180975"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -5948,7 +6465,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9697720" y="30111700"/>
+              <a:off x="10370820" y="33283525"/>
               <a:ext cx="1143635" cy="180975"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -5989,7 +6506,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9697720" y="30978475"/>
+              <a:off x="10370820" y="34299525"/>
               <a:ext cx="1143635" cy="180975"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -6030,7 +6547,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9697720" y="31188025"/>
+              <a:off x="10370820" y="35105975"/>
               <a:ext cx="1143635" cy="180975"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -6071,7 +6588,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9697720" y="31397575"/>
+              <a:off x="10370820" y="35912425"/>
               <a:ext cx="1143635" cy="180975"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -6112,7 +6629,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9697720" y="31607125"/>
+              <a:off x="10370820" y="36718875"/>
               <a:ext cx="1143635" cy="180975"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -6137,8 +6654,8 @@
         <xdr:to>
           <xdr:col>4</xdr:col>
           <xdr:colOff>1143635</xdr:colOff>
-          <xdr:row>47</xdr:row>
-          <xdr:rowOff>9525</xdr:rowOff>
+          <xdr:row>46</xdr:row>
+          <xdr:rowOff>180975</xdr:rowOff>
         </xdr:to>
         <xdr:sp>
           <xdr:nvSpPr>
@@ -6153,7 +6670,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9697720" y="31816675"/>
+              <a:off x="10370820" y="37525325"/>
               <a:ext cx="1143635" cy="180975"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -6178,8 +6695,8 @@
         <xdr:to>
           <xdr:col>4</xdr:col>
           <xdr:colOff>1143635</xdr:colOff>
-          <xdr:row>48</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
+          <xdr:row>47</xdr:row>
+          <xdr:rowOff>180975</xdr:rowOff>
         </xdr:to>
         <xdr:sp>
           <xdr:nvSpPr>
@@ -6194,7 +6711,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9697720" y="31988125"/>
+              <a:off x="10370820" y="38331775"/>
               <a:ext cx="1143635" cy="180975"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -6213,14 +6730,14 @@
         <xdr:from>
           <xdr:col>4</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>48</xdr:row>
+          <xdr:row>58</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>4</xdr:col>
           <xdr:colOff>1143635</xdr:colOff>
-          <xdr:row>49</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
+          <xdr:row>58</xdr:row>
+          <xdr:rowOff>180975</xdr:rowOff>
         </xdr:to>
         <xdr:sp>
           <xdr:nvSpPr>
@@ -6235,7 +6752,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9697720" y="32169100"/>
+              <a:off x="10370820" y="46574075"/>
               <a:ext cx="1143635" cy="180975"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -6254,14 +6771,14 @@
         <xdr:from>
           <xdr:col>4</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>49</xdr:row>
+          <xdr:row>59</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>4</xdr:col>
           <xdr:colOff>1143635</xdr:colOff>
-          <xdr:row>50</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
+          <xdr:row>59</xdr:row>
+          <xdr:rowOff>180975</xdr:rowOff>
         </xdr:to>
         <xdr:sp>
           <xdr:nvSpPr>
@@ -6276,7 +6793,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9697720" y="32350075"/>
+              <a:off x="10370820" y="47170975"/>
               <a:ext cx="1143635" cy="180975"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -6295,14 +6812,14 @@
         <xdr:from>
           <xdr:col>4</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>50</xdr:row>
+          <xdr:row>60</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>4</xdr:col>
           <xdr:colOff>1143635</xdr:colOff>
-          <xdr:row>51</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
+          <xdr:row>60</xdr:row>
+          <xdr:rowOff>180975</xdr:rowOff>
         </xdr:to>
         <xdr:sp>
           <xdr:nvSpPr>
@@ -6317,7 +6834,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9697720" y="32531050"/>
+              <a:off x="10370820" y="47767875"/>
               <a:ext cx="1143635" cy="180975"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -6336,14 +6853,14 @@
         <xdr:from>
           <xdr:col>4</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>53</xdr:row>
+          <xdr:row>48</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>4</xdr:col>
           <xdr:colOff>1143635</xdr:colOff>
-          <xdr:row>54</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
+          <xdr:row>48</xdr:row>
+          <xdr:rowOff>180975</xdr:rowOff>
         </xdr:to>
         <xdr:sp>
           <xdr:nvSpPr>
@@ -6358,7 +6875,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9697720" y="33073975"/>
+              <a:off x="10370820" y="39138225"/>
               <a:ext cx="1143635" cy="180975"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -6377,14 +6894,14 @@
         <xdr:from>
           <xdr:col>4</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>54</xdr:row>
+          <xdr:row>49</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>4</xdr:col>
           <xdr:colOff>1143635</xdr:colOff>
-          <xdr:row>55</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
+          <xdr:row>49</xdr:row>
+          <xdr:rowOff>180975</xdr:rowOff>
         </xdr:to>
         <xdr:sp>
           <xdr:nvSpPr>
@@ -6399,7 +6916,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9697720" y="33254950"/>
+              <a:off x="10370820" y="39944675"/>
               <a:ext cx="1143635" cy="180975"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -6418,14 +6935,14 @@
         <xdr:from>
           <xdr:col>4</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>55</xdr:row>
+          <xdr:row>50</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>4</xdr:col>
           <xdr:colOff>1143635</xdr:colOff>
-          <xdr:row>56</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
+          <xdr:row>50</xdr:row>
+          <xdr:rowOff>180975</xdr:rowOff>
         </xdr:to>
         <xdr:sp>
           <xdr:nvSpPr>
@@ -6440,7 +6957,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9697720" y="33435925"/>
+              <a:off x="10370820" y="40751125"/>
               <a:ext cx="1143635" cy="180975"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -6459,14 +6976,14 @@
         <xdr:from>
           <xdr:col>4</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>56</xdr:row>
+          <xdr:row>51</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>4</xdr:col>
           <xdr:colOff>1143635</xdr:colOff>
-          <xdr:row>57</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
+          <xdr:row>51</xdr:row>
+          <xdr:rowOff>180975</xdr:rowOff>
         </xdr:to>
         <xdr:sp>
           <xdr:nvSpPr>
@@ -6481,7 +6998,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9697720" y="33616900"/>
+              <a:off x="10370820" y="41557575"/>
               <a:ext cx="1143635" cy="180975"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -6500,14 +7017,14 @@
         <xdr:from>
           <xdr:col>4</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>57</xdr:row>
+          <xdr:row>52</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>4</xdr:col>
           <xdr:colOff>1143635</xdr:colOff>
-          <xdr:row>58</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
+          <xdr:row>52</xdr:row>
+          <xdr:rowOff>180975</xdr:rowOff>
         </xdr:to>
         <xdr:sp>
           <xdr:nvSpPr>
@@ -6522,7 +7039,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9697720" y="33797875"/>
+              <a:off x="10370820" y="42364025"/>
               <a:ext cx="1143635" cy="180975"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -6541,14 +7058,14 @@
         <xdr:from>
           <xdr:col>4</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>58</xdr:row>
+          <xdr:row>53</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>4</xdr:col>
           <xdr:colOff>1143635</xdr:colOff>
-          <xdr:row>59</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
+          <xdr:row>53</xdr:row>
+          <xdr:rowOff>180975</xdr:rowOff>
         </xdr:to>
         <xdr:sp>
           <xdr:nvSpPr>
@@ -6563,7 +7080,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9697720" y="33978850"/>
+              <a:off x="10370820" y="43170475"/>
               <a:ext cx="1143635" cy="180975"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -6582,14 +7099,14 @@
         <xdr:from>
           <xdr:col>4</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>59</xdr:row>
+          <xdr:row>54</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>4</xdr:col>
           <xdr:colOff>1143635</xdr:colOff>
-          <xdr:row>60</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
+          <xdr:row>54</xdr:row>
+          <xdr:rowOff>180975</xdr:rowOff>
         </xdr:to>
         <xdr:sp>
           <xdr:nvSpPr>
@@ -6604,7 +7121,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9697720" y="34159825"/>
+              <a:off x="10370820" y="43976925"/>
               <a:ext cx="1143635" cy="180975"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -6623,14 +7140,14 @@
         <xdr:from>
           <xdr:col>4</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>60</xdr:row>
+          <xdr:row>55</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>4</xdr:col>
           <xdr:colOff>1143635</xdr:colOff>
-          <xdr:row>61</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
+          <xdr:row>55</xdr:row>
+          <xdr:rowOff>180975</xdr:rowOff>
         </xdr:to>
         <xdr:sp>
           <xdr:nvSpPr>
@@ -6645,7 +7162,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9697720" y="34340800"/>
+              <a:off x="10370820" y="44783375"/>
               <a:ext cx="1143635" cy="180975"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -6664,14 +7181,14 @@
         <xdr:from>
           <xdr:col>4</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>61</xdr:row>
+          <xdr:row>56</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>4</xdr:col>
           <xdr:colOff>1143635</xdr:colOff>
-          <xdr:row>62</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
+          <xdr:row>56</xdr:row>
+          <xdr:rowOff>180975</xdr:rowOff>
         </xdr:to>
         <xdr:sp>
           <xdr:nvSpPr>
@@ -6686,7 +7203,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9697720" y="34521775"/>
+              <a:off x="10370820" y="45380275"/>
               <a:ext cx="1143635" cy="180975"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -6705,14 +7222,14 @@
         <xdr:from>
           <xdr:col>4</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>62</xdr:row>
+          <xdr:row>57</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>4</xdr:col>
           <xdr:colOff>1143635</xdr:colOff>
-          <xdr:row>63</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
+          <xdr:row>57</xdr:row>
+          <xdr:rowOff>180975</xdr:rowOff>
         </xdr:to>
         <xdr:sp>
           <xdr:nvSpPr>
@@ -6727,7 +7244,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9697720" y="34702750"/>
+              <a:off x="10370820" y="45977175"/>
               <a:ext cx="1143635" cy="180975"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -6744,23 +7261,23 @@
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
-          <xdr:col>4</xdr:col>
+          <xdr:col>5</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>63</xdr:row>
+          <xdr:row>67</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
-          <xdr:col>4</xdr:col>
-          <xdr:colOff>1143635</xdr:colOff>
-          <xdr:row>64</xdr:row>
+          <xdr:col>5</xdr:col>
+          <xdr:colOff>1448435</xdr:colOff>
+          <xdr:row>68</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp>
           <xdr:nvSpPr>
-            <xdr:cNvPr id="1115" name="Host Control  91" hidden="1">
+            <xdr:cNvPr id="1116" name="Host Control  92" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1115"/>
+                  <a14:compatExt spid="_x0000_s1116"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -6768,8 +7285,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9697720" y="34883725"/>
-              <a:ext cx="1143635" cy="180975"/>
+              <a:off x="11819255" y="50085625"/>
+              <a:ext cx="1448435" cy="180975"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -6798,10 +7315,10 @@
         </xdr:to>
         <xdr:sp>
           <xdr:nvSpPr>
-            <xdr:cNvPr id="1116" name="Host Control  92" hidden="1">
+            <xdr:cNvPr id="1117" name="Host Control  93" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1116"/>
+                  <a14:compatExt spid="_x0000_s1117"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -6809,7 +7326,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="11146155" y="35788600"/>
+              <a:off x="11819255" y="50266600"/>
               <a:ext cx="1448435" cy="180975"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -6839,10 +7356,10 @@
         </xdr:to>
         <xdr:sp>
           <xdr:nvSpPr>
-            <xdr:cNvPr id="1117" name="Host Control  93" hidden="1">
+            <xdr:cNvPr id="1118" name="Host Control  94" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1117"/>
+                  <a14:compatExt spid="_x0000_s1118"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -6850,7 +7367,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="11146155" y="35969575"/>
+              <a:off x="11819255" y="50447575"/>
               <a:ext cx="1448435" cy="180975"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -6880,47 +7397,6 @@
         </xdr:to>
         <xdr:sp>
           <xdr:nvSpPr>
-            <xdr:cNvPr id="1118" name="Host Control  94" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1118"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="11146155" y="36150550"/>
-              <a:ext cx="1448435" cy="180975"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-          </xdr:spPr>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>5</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>71</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>5</xdr:col>
-          <xdr:colOff>1448435</xdr:colOff>
-          <xdr:row>72</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp>
-          <xdr:nvSpPr>
             <xdr:cNvPr id="1119" name="Host Control  95" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
@@ -6932,7 +7408,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="11146155" y="36331525"/>
+              <a:off x="11819255" y="50628550"/>
               <a:ext cx="1448435" cy="180975"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -7198,20 +7674,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R102"/>
+  <dimension ref="A1:R101"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="2" width="50.625" customWidth="1"/>
-    <col min="3" max="3" width="11.0083333333333" customWidth="1"/>
+    <col min="3" max="3" width="19.8416666666667" customWidth="1"/>
     <col min="4" max="4" width="15.0083333333333" customWidth="1"/>
     <col min="5" max="5" width="19.0083333333333" customWidth="1"/>
     <col min="6" max="6" width="50.625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="25.3416666666667" customWidth="1"/>
-    <col min="8" max="8" width="17.5" customWidth="1"/>
-    <col min="9" max="9" width="41.0083333333333" customWidth="1"/>
-    <col min="10" max="10" width="21.4583333333333" customWidth="1"/>
-    <col min="11" max="15" width="50.625" customWidth="1"/>
-    <col min="16" max="16" width="23.3416666666667" customWidth="1"/>
+    <col min="7" max="7" width="11.0083333333333" customWidth="1"/>
+    <col min="8" max="8" width="15.675" customWidth="1"/>
+    <col min="9" max="9" width="46.3416666666667" customWidth="1"/>
+    <col min="10" max="10" width="20.5083333333333" customWidth="1"/>
+    <col min="11" max="11" width="28.675" customWidth="1"/>
+    <col min="12" max="15" width="50.625" customWidth="1"/>
+    <col min="16" max="16" width="33.175" customWidth="1"/>
     <col min="17" max="17" width="50.625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -7280,10 +7757,10 @@
         <v>19</v>
       </c>
       <c r="D2" s="5"/>
-      <c r="E2" s="29" t="s">
+      <c r="E2" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="F2" s="30" t="s">
+      <c r="F2" s="33" t="s">
         <v>21</v>
       </c>
       <c r="G2" s="5" t="s">
@@ -7295,16 +7772,16 @@
       <c r="I2" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="K2" s="6" t="s">
+      <c r="K2" s="5" t="s">
         <v>25</v>
       </c>
       <c r="L2" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="M2" s="6" t="s">
+      <c r="M2" s="5" t="s">
         <v>27</v>
       </c>
       <c r="N2" s="6" t="s">
@@ -7346,16 +7823,16 @@
       <c r="I3" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="J3" t="s">
+      <c r="J3" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="K3" s="6" t="s">
+      <c r="K3" s="5" t="s">
         <v>37</v>
       </c>
       <c r="L3" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="M3" s="6" t="s">
+      <c r="M3" s="5" t="s">
         <v>39</v>
       </c>
       <c r="N3" s="6" t="s">
@@ -7385,7 +7862,7 @@
       <c r="E4" s="5">
         <v>50881</v>
       </c>
-      <c r="F4" s="30" t="s">
+      <c r="F4" s="33" t="s">
         <v>46</v>
       </c>
       <c r="G4" s="5" t="s">
@@ -7397,16 +7874,16 @@
       <c r="I4" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="J4" t="s">
+      <c r="J4" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="K4" s="6" t="s">
+      <c r="K4" s="5" t="s">
         <v>49</v>
       </c>
       <c r="L4" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="M4" s="6" t="s">
+      <c r="M4" s="5" t="s">
         <v>51</v>
       </c>
       <c r="N4" s="6" t="s">
@@ -7436,7 +7913,7 @@
       <c r="E5" s="5">
         <v>50879</v>
       </c>
-      <c r="F5" s="30" t="s">
+      <c r="F5" s="33" t="s">
         <v>58</v>
       </c>
       <c r="G5" s="5" t="s">
@@ -7448,16 +7925,16 @@
       <c r="I5" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="J5" t="s">
+      <c r="J5" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="K5" s="6" t="s">
+      <c r="K5" s="5" t="s">
         <v>61</v>
       </c>
       <c r="L5" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="M5" s="6" t="s">
+      <c r="M5" s="5" t="s">
         <v>63</v>
       </c>
       <c r="N5" s="6" t="s">
@@ -7487,7 +7964,7 @@
       <c r="E6" s="5">
         <v>50882</v>
       </c>
-      <c r="F6" s="30" t="s">
+      <c r="F6" s="33" t="s">
         <v>70</v>
       </c>
       <c r="G6" s="5" t="s">
@@ -7499,16 +7976,16 @@
       <c r="I6" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="J6" t="s">
+      <c r="J6" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="K6" s="6" t="s">
+      <c r="K6" s="5" t="s">
         <v>73</v>
       </c>
       <c r="L6" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="M6" s="6" t="s">
+      <c r="M6" s="5" t="s">
         <v>75</v>
       </c>
       <c r="N6" s="6" t="s">
@@ -7535,10 +8012,10 @@
         <v>82</v>
       </c>
       <c r="D7" s="5"/>
-      <c r="E7" s="9">
+      <c r="E7" s="10">
         <v>49977</v>
       </c>
-      <c r="F7" s="30" t="s">
+      <c r="F7" s="33" t="s">
         <v>83</v>
       </c>
       <c r="G7" s="5" t="s">
@@ -7550,16 +8027,16 @@
       <c r="I7" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="J7" t="s">
+      <c r="J7" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="K7" s="6" t="s">
+      <c r="K7" s="5" t="s">
         <v>86</v>
       </c>
       <c r="L7" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="M7" s="6" t="s">
+      <c r="M7" s="5" t="s">
         <v>88</v>
       </c>
       <c r="N7" s="6" t="s">
@@ -7589,7 +8066,7 @@
       <c r="E8" s="5">
         <v>49976</v>
       </c>
-      <c r="F8" s="30" t="s">
+      <c r="F8" s="33" t="s">
         <v>95</v>
       </c>
       <c r="G8" s="5" t="s">
@@ -7601,16 +8078,16 @@
       <c r="I8" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="J8" t="s">
+      <c r="J8" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="K8" s="6" t="s">
+      <c r="K8" s="5" t="s">
         <v>98</v>
       </c>
       <c r="L8" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="M8" s="6" t="s">
+      <c r="M8" s="5" t="s">
         <v>100</v>
       </c>
       <c r="N8" s="6" t="s">
@@ -7640,7 +8117,7 @@
       <c r="E9" s="5">
         <v>49973</v>
       </c>
-      <c r="F9" s="30" t="s">
+      <c r="F9" s="33" t="s">
         <v>107</v>
       </c>
       <c r="G9" s="5" t="s">
@@ -7652,16 +8129,16 @@
       <c r="I9" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="J9" t="s">
+      <c r="J9" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="K9" s="6" t="s">
+      <c r="K9" s="5" t="s">
         <v>109</v>
       </c>
       <c r="L9" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="M9" s="6" t="s">
+      <c r="M9" s="5" t="s">
         <v>111</v>
       </c>
       <c r="N9" s="6" t="s">
@@ -7691,7 +8168,7 @@
       <c r="E10" s="5">
         <v>49975</v>
       </c>
-      <c r="F10" s="30" t="s">
+      <c r="F10" s="33" t="s">
         <v>118</v>
       </c>
       <c r="G10" s="5" t="s">
@@ -7703,16 +8180,16 @@
       <c r="I10" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="J10" t="s">
+      <c r="J10" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="K10" s="6" t="s">
+      <c r="K10" s="5" t="s">
         <v>121</v>
       </c>
       <c r="L10" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="M10" s="6" t="s">
+      <c r="M10" s="5" t="s">
         <v>123</v>
       </c>
       <c r="N10" s="6" t="s">
@@ -7742,7 +8219,7 @@
       <c r="E11" s="5">
         <v>49974</v>
       </c>
-      <c r="F11" s="30" t="s">
+      <c r="F11" s="33" t="s">
         <v>130</v>
       </c>
       <c r="G11" s="5" t="s">
@@ -7754,16 +8231,16 @@
       <c r="I11" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="J11" t="s">
+      <c r="J11" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="K11" s="6" t="s">
+      <c r="K11" s="5" t="s">
         <v>132</v>
       </c>
       <c r="L11" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="M11" s="6" t="s">
+      <c r="M11" s="5" t="s">
         <v>134</v>
       </c>
       <c r="N11" s="6" t="s">
@@ -7793,7 +8270,7 @@
       <c r="E12" s="5">
         <v>50529</v>
       </c>
-      <c r="F12" s="30" t="s">
+      <c r="F12" s="33" t="s">
         <v>142</v>
       </c>
       <c r="G12" s="5" t="s">
@@ -7805,16 +8282,16 @@
       <c r="I12" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="J12" t="s">
+      <c r="J12" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="K12" s="6" t="s">
+      <c r="K12" s="5" t="s">
         <v>144</v>
       </c>
       <c r="L12" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="M12" s="6" t="s">
+      <c r="M12" s="5" t="s">
         <v>146</v>
       </c>
       <c r="N12" s="6" t="s">
@@ -7856,16 +8333,16 @@
       <c r="I13" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="J13" t="s">
+      <c r="J13" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="K13" s="6" t="s">
+      <c r="K13" s="5" t="s">
         <v>155</v>
       </c>
       <c r="L13" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="M13" s="6" t="s">
+      <c r="M13" s="5" t="s">
         <v>157</v>
       </c>
       <c r="N13" s="6" t="s">
@@ -7907,16 +8384,16 @@
       <c r="I14" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="J14" t="s">
+      <c r="J14" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="K14" s="6" t="s">
+      <c r="K14" s="5" t="s">
         <v>166</v>
       </c>
       <c r="L14" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="M14" s="6" t="s">
+      <c r="M14" s="5" t="s">
         <v>168</v>
       </c>
       <c r="N14" s="6" t="s">
@@ -7958,16 +8435,16 @@
       <c r="I15" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="J15" t="s">
+      <c r="J15" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="K15" s="6" t="s">
+      <c r="K15" s="5" t="s">
         <v>177</v>
       </c>
       <c r="L15" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="M15" s="6" t="s">
+      <c r="M15" s="5" t="s">
         <v>179</v>
       </c>
       <c r="N15" s="6" t="s">
@@ -7997,7 +8474,7 @@
       <c r="E16" s="5">
         <v>50532</v>
       </c>
-      <c r="F16" s="30" t="s">
+      <c r="F16" s="33" t="s">
         <v>186</v>
       </c>
       <c r="G16" s="5" t="s">
@@ -8009,16 +8486,16 @@
       <c r="I16" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="J16" t="s">
+      <c r="J16" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="K16" s="6" t="s">
+      <c r="K16" s="5" t="s">
         <v>188</v>
       </c>
       <c r="L16" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="M16" s="6" t="s">
+      <c r="M16" s="5" t="s">
         <v>190</v>
       </c>
       <c r="N16" s="6" t="s">
@@ -8034,21 +8511,21 @@
         <v>194</v>
       </c>
     </row>
-    <row r="17" ht="30.5" customHeight="1" spans="1:18">
-      <c r="A17" s="10" t="s">
+    <row r="17" ht="63.5" customHeight="1" spans="1:18">
+      <c r="A17" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="B17" s="10" t="s">
+      <c r="B17" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="C17" s="10" t="s">
+      <c r="C17" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="D17" s="10"/>
-      <c r="E17" s="10">
+      <c r="D17" s="11"/>
+      <c r="E17" s="11">
         <v>51843</v>
       </c>
-      <c r="F17" s="11" t="s">
+      <c r="F17" s="7" t="s">
         <v>198</v>
       </c>
       <c r="G17" s="5" t="s">
@@ -8057,49 +8534,49 @@
       <c r="H17" s="8">
         <v>46173</v>
       </c>
-      <c r="I17" s="10" t="s">
+      <c r="I17" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="J17" t="s">
+      <c r="J17" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="K17" s="12" t="s">
+      <c r="K17" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="L17" s="4" t="s">
+      <c r="L17" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="M17" s="4" t="s">
+      <c r="M17" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="N17" s="4" t="s">
+      <c r="N17" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="O17" s="4" t="s">
+      <c r="O17" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="P17" s="4" t="s">
+      <c r="P17" s="5" t="s">
         <v>205</v>
       </c>
-      <c r="Q17" s="4" t="s">
+      <c r="Q17" s="6" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="18" ht="30.5" customHeight="1" spans="1:18">
-      <c r="A18" s="10" t="s">
+    <row r="18" ht="63.5" customHeight="1" spans="1:18">
+      <c r="A18" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="B18" s="10" t="s">
+      <c r="B18" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="C18" s="10" t="s">
+      <c r="C18" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="D18" s="10"/>
-      <c r="E18" s="10">
+      <c r="D18" s="11"/>
+      <c r="E18" s="11">
         <v>51844</v>
       </c>
-      <c r="F18" s="11" t="s">
+      <c r="F18" s="7" t="s">
         <v>209</v>
       </c>
       <c r="G18" s="5" t="s">
@@ -8108,49 +8585,49 @@
       <c r="H18" s="8">
         <v>46173</v>
       </c>
-      <c r="I18" s="10" t="s">
+      <c r="I18" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="J18" t="s">
+      <c r="J18" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="K18" s="12" t="s">
+      <c r="K18" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="L18" s="4" t="s">
+      <c r="L18" s="6" t="s">
         <v>212</v>
       </c>
-      <c r="M18" s="4" t="s">
+      <c r="M18" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="N18" s="4" t="s">
+      <c r="N18" s="6" t="s">
         <v>214</v>
       </c>
-      <c r="O18" s="4" t="s">
+      <c r="O18" s="6" t="s">
         <v>215</v>
       </c>
-      <c r="P18" s="4" t="s">
+      <c r="P18" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="Q18" s="4" t="s">
+      <c r="Q18" s="6" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="19" ht="30.5" customHeight="1" spans="1:18">
-      <c r="A19" s="10" t="s">
+    <row r="19" ht="63.5" customHeight="1" spans="1:18">
+      <c r="A19" s="5" t="s">
         <v>218</v>
       </c>
-      <c r="B19" s="10" t="s">
+      <c r="B19" s="6" t="s">
         <v>219</v>
       </c>
-      <c r="C19" s="10" t="s">
+      <c r="C19" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="D19" s="10"/>
-      <c r="E19" s="10">
+      <c r="D19" s="11"/>
+      <c r="E19" s="11">
         <v>51845</v>
       </c>
-      <c r="F19" s="11" t="s">
+      <c r="F19" s="7" t="s">
         <v>220</v>
       </c>
       <c r="G19" s="5" t="s">
@@ -8159,50 +8636,50 @@
       <c r="H19" s="8">
         <v>46173</v>
       </c>
-      <c r="I19" s="10" t="s">
+      <c r="I19" s="5" t="s">
         <v>221</v>
       </c>
-      <c r="J19" t="s">
+      <c r="J19" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="K19" s="12" t="s">
+      <c r="K19" s="5" t="s">
         <v>222</v>
       </c>
-      <c r="L19" s="4" t="s">
+      <c r="L19" s="6" t="s">
         <v>223</v>
       </c>
-      <c r="M19" s="4" t="s">
+      <c r="M19" s="5" t="s">
         <v>224</v>
       </c>
-      <c r="N19" s="4" t="s">
+      <c r="N19" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="O19" s="4" t="s">
+      <c r="O19" s="6" t="s">
         <v>226</v>
       </c>
-      <c r="P19" s="4" t="s">
+      <c r="P19" s="5" t="s">
         <v>227</v>
       </c>
-      <c r="Q19" s="4" t="s">
+      <c r="Q19" s="6" t="s">
         <v>228</v>
       </c>
       <c r="R19" s="4"/>
     </row>
-    <row r="20" ht="63.5" customHeight="1" spans="1:18">
-      <c r="A20" s="10" t="s">
+    <row r="20" ht="47" customHeight="1" spans="1:18">
+      <c r="A20" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="B20" s="10" t="s">
+      <c r="B20" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="C20" s="10" t="s">
+      <c r="C20" s="5" t="s">
         <v>231</v>
       </c>
-      <c r="D20" s="10"/>
-      <c r="E20" s="10">
+      <c r="D20" s="11"/>
+      <c r="E20" s="11">
         <v>51513</v>
       </c>
-      <c r="F20" s="11" t="s">
+      <c r="F20" s="7" t="s">
         <v>232</v>
       </c>
       <c r="G20" s="5" t="s">
@@ -8211,50 +8688,50 @@
       <c r="H20" s="8">
         <v>46173</v>
       </c>
-      <c r="I20" s="10" t="s">
+      <c r="I20" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="J20" t="s">
+      <c r="J20" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="K20" s="12" t="s">
+      <c r="K20" s="5" t="s">
         <v>234</v>
       </c>
-      <c r="L20" s="4" t="s">
+      <c r="L20" s="6" t="s">
         <v>235</v>
       </c>
-      <c r="M20" s="4" t="s">
+      <c r="M20" s="5" t="s">
         <v>236</v>
       </c>
-      <c r="N20" s="4" t="s">
+      <c r="N20" s="6" t="s">
         <v>237</v>
       </c>
-      <c r="O20" s="4" t="s">
+      <c r="O20" s="6" t="s">
         <v>238</v>
       </c>
-      <c r="P20" s="4" t="s">
+      <c r="P20" s="5" t="s">
         <v>239</v>
       </c>
-      <c r="Q20" s="4" t="s">
+      <c r="Q20" s="6" t="s">
         <v>240</v>
       </c>
-      <c r="R20" s="13"/>
+      <c r="R20" s="12"/>
     </row>
-    <row r="21" ht="63.5" customHeight="1" spans="1:18">
-      <c r="A21" s="10" t="s">
+    <row r="21" ht="47" customHeight="1" spans="1:18">
+      <c r="A21" s="5" t="s">
         <v>241</v>
       </c>
-      <c r="B21" s="10" t="s">
+      <c r="B21" s="6" t="s">
         <v>242</v>
       </c>
-      <c r="C21" s="10" t="s">
+      <c r="C21" s="5" t="s">
         <v>231</v>
       </c>
-      <c r="D21" s="10"/>
-      <c r="E21" s="10">
+      <c r="D21" s="11"/>
+      <c r="E21" s="11">
         <v>51512</v>
       </c>
-      <c r="F21" s="11" t="s">
+      <c r="F21" s="7" t="s">
         <v>243</v>
       </c>
       <c r="G21" s="5" t="s">
@@ -8263,49 +8740,49 @@
       <c r="H21" s="8">
         <v>46173</v>
       </c>
-      <c r="I21" s="10" t="s">
+      <c r="I21" s="5" t="s">
         <v>244</v>
       </c>
-      <c r="J21" t="s">
+      <c r="J21" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="K21" s="12" t="s">
+      <c r="K21" s="5" t="s">
         <v>245</v>
       </c>
-      <c r="L21" s="4" t="s">
+      <c r="L21" s="6" t="s">
         <v>246</v>
       </c>
-      <c r="M21" s="4" t="s">
+      <c r="M21" s="5" t="s">
         <v>247</v>
       </c>
-      <c r="N21" s="4" t="s">
+      <c r="N21" s="6" t="s">
         <v>248</v>
       </c>
-      <c r="O21" s="4" t="s">
+      <c r="O21" s="6" t="s">
         <v>249</v>
       </c>
-      <c r="P21" s="4" t="s">
+      <c r="P21" s="5" t="s">
         <v>250</v>
       </c>
-      <c r="Q21" s="4" t="s">
+      <c r="Q21" s="6" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="22" ht="63.5" customHeight="1" spans="1:18">
-      <c r="A22" s="10" t="s">
+    <row r="22" ht="47" customHeight="1" spans="1:18">
+      <c r="A22" s="5" t="s">
         <v>252</v>
       </c>
-      <c r="B22" s="10" t="s">
+      <c r="B22" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="C22" s="10" t="s">
+      <c r="C22" s="5" t="s">
         <v>231</v>
       </c>
-      <c r="D22" s="10"/>
-      <c r="E22" s="10">
+      <c r="D22" s="11"/>
+      <c r="E22" s="11">
         <v>51514</v>
       </c>
-      <c r="F22" s="11" t="s">
+      <c r="F22" s="7" t="s">
         <v>254</v>
       </c>
       <c r="G22" s="5" t="s">
@@ -8314,231 +8791,237 @@
       <c r="H22" s="8">
         <v>46173</v>
       </c>
-      <c r="I22" s="10" t="s">
+      <c r="I22" s="5" t="s">
         <v>255</v>
       </c>
-      <c r="J22" t="s">
+      <c r="J22" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="K22" s="12" t="s">
+      <c r="K22" s="5" t="s">
         <v>256</v>
       </c>
-      <c r="L22" s="4" t="s">
+      <c r="L22" s="6" t="s">
         <v>257</v>
       </c>
-      <c r="M22" s="4" t="s">
+      <c r="M22" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="N22" s="4" t="s">
+      <c r="N22" s="6" t="s">
         <v>259</v>
       </c>
-      <c r="O22" s="4" t="s">
+      <c r="O22" s="6" t="s">
         <v>260</v>
       </c>
-      <c r="P22" s="4" t="s">
+      <c r="P22" s="5" t="s">
         <v>261</v>
       </c>
-      <c r="Q22" s="4" t="s">
+      <c r="Q22" s="6" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="23" ht="63.5" customHeight="1" spans="1:18">
-      <c r="A23" s="10" t="s">
+    <row r="23" ht="47" customHeight="1" spans="1:18">
+      <c r="A23" s="5" t="s">
         <v>263</v>
       </c>
-      <c r="B23" s="10" t="s">
+      <c r="B23" s="6" t="s">
         <v>264</v>
       </c>
-      <c r="C23" s="10" t="s">
+      <c r="C23" s="5" t="s">
         <v>231</v>
       </c>
-      <c r="D23" s="10"/>
-      <c r="E23" s="10">
+      <c r="D23" s="11"/>
+      <c r="E23" s="11">
         <v>51517</v>
       </c>
-      <c r="F23" s="11" t="s">
+      <c r="F23" s="7" t="s">
         <v>265</v>
       </c>
       <c r="G23" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="H23" s="10"/>
-      <c r="I23" s="10" t="s">
+      <c r="H23" s="11"/>
+      <c r="I23" s="5" t="s">
         <v>255</v>
       </c>
-      <c r="K23" s="12" t="s">
+      <c r="J23" s="13"/>
+      <c r="K23" s="5" t="s">
         <v>266</v>
       </c>
-      <c r="L23" s="4" t="s">
+      <c r="L23" s="6" t="s">
         <v>267</v>
       </c>
-      <c r="M23" s="4" t="s">
+      <c r="M23" s="5" t="s">
         <v>268</v>
       </c>
-      <c r="N23" s="4" t="s">
+      <c r="N23" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="O23" s="4" t="s">
+      <c r="O23" s="6" t="s">
         <v>270</v>
       </c>
-      <c r="P23" s="4" t="s">
+      <c r="P23" s="5" t="s">
         <v>271</v>
       </c>
-      <c r="Q23" s="4" t="s">
+      <c r="Q23" s="6" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="24" ht="40.5" spans="1:18">
-      <c r="A24" s="10" t="s">
+    <row r="24" ht="47" customHeight="1" spans="1:18">
+      <c r="A24" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="B24" s="10" t="s">
+      <c r="B24" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="C24" s="10" t="s">
+      <c r="C24" s="5" t="s">
         <v>231</v>
       </c>
-      <c r="D24" s="10"/>
-      <c r="E24" s="10">
+      <c r="D24" s="11"/>
+      <c r="E24" s="11">
         <v>51515</v>
       </c>
-      <c r="F24" s="11" t="s">
+      <c r="F24" s="7" t="s">
         <v>275</v>
       </c>
       <c r="G24" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="H24" s="10"/>
-      <c r="I24" s="10" t="s">
+      <c r="H24" s="11"/>
+      <c r="I24" s="5" t="s">
         <v>276</v>
       </c>
-      <c r="K24" s="12" t="s">
+      <c r="J24" s="13"/>
+      <c r="K24" s="5" t="s">
         <v>277</v>
       </c>
-      <c r="L24" s="4" t="s">
+      <c r="L24" s="6" t="s">
         <v>278</v>
       </c>
-      <c r="M24" s="4" t="s">
+      <c r="M24" s="5" t="s">
         <v>279</v>
       </c>
-      <c r="N24" s="4" t="s">
+      <c r="N24" s="6" t="s">
         <v>280</v>
       </c>
-      <c r="O24" s="4" t="s">
+      <c r="O24" s="6" t="s">
         <v>281</v>
       </c>
-      <c r="P24" s="4" t="s">
+      <c r="P24" s="5" t="s">
         <v>282</v>
       </c>
-      <c r="Q24" s="4" t="s">
+      <c r="Q24" s="6" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="25" ht="40.5" spans="1:18">
-      <c r="A25" s="10" t="s">
+    <row r="25" ht="47" customHeight="1" spans="1:18">
+      <c r="A25" s="5" t="s">
         <v>284</v>
       </c>
-      <c r="B25" s="10" t="s">
+      <c r="B25" s="6" t="s">
         <v>285</v>
       </c>
-      <c r="C25" s="10" t="s">
+      <c r="C25" s="5" t="s">
         <v>231</v>
       </c>
-      <c r="D25" s="10"/>
-      <c r="E25" s="10">
+      <c r="D25" s="11"/>
+      <c r="E25" s="11">
         <v>51516</v>
       </c>
-      <c r="F25" s="1" t="s">
+      <c r="F25" s="14" t="s">
         <v>286</v>
       </c>
       <c r="G25" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="I25" t="s">
+      <c r="H25" s="13"/>
+      <c r="I25" s="9" t="s">
         <v>287</v>
       </c>
-      <c r="K25" s="12" t="s">
+      <c r="J25" s="13"/>
+      <c r="K25" s="5" t="s">
         <v>288</v>
       </c>
-      <c r="L25" s="4" t="s">
+      <c r="L25" s="6" t="s">
         <v>289</v>
       </c>
-      <c r="M25" s="4" t="s">
+      <c r="M25" s="5" t="s">
         <v>290</v>
       </c>
-      <c r="N25" s="4" t="s">
+      <c r="N25" s="6" t="s">
         <v>291</v>
       </c>
-      <c r="O25" s="4" t="s">
+      <c r="O25" s="6" t="s">
         <v>292</v>
       </c>
-      <c r="P25" s="4" t="s">
+      <c r="P25" s="5" t="s">
         <v>293</v>
       </c>
-      <c r="Q25" s="4" t="s">
+      <c r="Q25" s="6" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="26" ht="40.5" spans="1:18">
-      <c r="A26" s="10" t="s">
+    <row r="26" ht="47" customHeight="1" spans="1:18">
+      <c r="A26" s="5" t="s">
         <v>295</v>
       </c>
-      <c r="B26" s="10" t="s">
+      <c r="B26" s="6" t="s">
         <v>296</v>
       </c>
-      <c r="C26" s="10" t="s">
+      <c r="C26" s="5" t="s">
         <v>297</v>
       </c>
-      <c r="D26" s="10"/>
-      <c r="E26" s="10">
+      <c r="D26" s="11"/>
+      <c r="E26" s="11">
         <v>51894</v>
       </c>
-      <c r="F26" s="1" t="s">
+      <c r="F26" s="14" t="s">
         <v>298</v>
       </c>
       <c r="G26" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="I26" t="s">
+      <c r="H26" s="13"/>
+      <c r="I26" s="9" t="s">
         <v>299</v>
       </c>
-      <c r="K26" s="12" t="s">
+      <c r="J26" s="13"/>
+      <c r="K26" s="5" t="s">
         <v>300</v>
       </c>
-      <c r="L26" s="4" t="s">
+      <c r="L26" s="6" t="s">
         <v>301</v>
       </c>
-      <c r="M26" s="4" t="s">
+      <c r="M26" s="5" t="s">
         <v>302</v>
       </c>
-      <c r="N26" s="4" t="s">
+      <c r="N26" s="6" t="s">
         <v>303</v>
       </c>
-      <c r="O26" s="4" t="s">
+      <c r="O26" s="6" t="s">
         <v>304</v>
       </c>
-      <c r="P26" s="4" t="s">
+      <c r="P26" s="5" t="s">
         <v>305</v>
       </c>
-      <c r="Q26" s="4" t="s">
+      <c r="Q26" s="6" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="27" ht="40.5" spans="1:18">
+    <row r="27" ht="47" customHeight="1" spans="1:18">
       <c r="A27" s="5" t="s">
         <v>307</v>
       </c>
-      <c r="B27" s="10" t="s">
+      <c r="B27" s="6" t="s">
         <v>308</v>
       </c>
-      <c r="C27" s="10" t="s">
+      <c r="C27" s="5" t="s">
         <v>297</v>
       </c>
       <c r="D27" s="5"/>
       <c r="E27" s="5">
         <v>51895</v>
       </c>
-      <c r="F27" s="1" t="s">
+      <c r="F27" s="14" t="s">
         <v>309</v>
       </c>
       <c r="G27" s="5" t="s">
@@ -8547,80 +9030,82 @@
       <c r="H27" s="8">
         <v>46173</v>
       </c>
-      <c r="I27" t="s">
+      <c r="I27" s="9" t="s">
         <v>310</v>
       </c>
-      <c r="J27" t="s">
+      <c r="J27" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="K27" s="12" t="s">
+      <c r="K27" s="5" t="s">
         <v>311</v>
       </c>
-      <c r="L27" s="4" t="s">
+      <c r="L27" s="6" t="s">
         <v>312</v>
       </c>
-      <c r="M27" s="4" t="s">
+      <c r="M27" s="5" t="s">
         <v>313</v>
       </c>
-      <c r="N27" s="4" t="s">
+      <c r="N27" s="6" t="s">
         <v>314</v>
       </c>
-      <c r="O27" s="4" t="s">
+      <c r="O27" s="6" t="s">
         <v>315</v>
       </c>
-      <c r="P27" s="4" t="s">
+      <c r="P27" s="5" t="s">
         <v>316</v>
       </c>
-      <c r="Q27" s="4" t="s">
+      <c r="Q27" s="6" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="28" ht="40.5" spans="1:18">
+    <row r="28" ht="47" customHeight="1" spans="1:18">
       <c r="A28" s="5" t="s">
         <v>318</v>
       </c>
-      <c r="B28" s="10" t="s">
+      <c r="B28" s="6" t="s">
         <v>319</v>
       </c>
-      <c r="C28" s="10" t="s">
+      <c r="C28" s="5" t="s">
         <v>297</v>
       </c>
       <c r="D28" s="5"/>
       <c r="E28" s="5">
         <v>51912</v>
       </c>
-      <c r="F28" s="1" t="s">
+      <c r="F28" s="14" t="s">
         <v>320</v>
       </c>
       <c r="G28" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="I28" t="s">
+      <c r="H28" s="13"/>
+      <c r="I28" s="9" t="s">
         <v>321</v>
       </c>
-      <c r="K28" s="12" t="s">
+      <c r="J28" s="13"/>
+      <c r="K28" s="5" t="s">
         <v>322</v>
       </c>
-      <c r="L28" s="4" t="s">
+      <c r="L28" s="6" t="s">
         <v>323</v>
       </c>
-      <c r="M28" s="4" t="s">
+      <c r="M28" s="5" t="s">
         <v>324</v>
       </c>
-      <c r="N28" s="4" t="s">
+      <c r="N28" s="6" t="s">
         <v>325</v>
       </c>
-      <c r="O28" s="4" t="s">
+      <c r="O28" s="6" t="s">
         <v>326</v>
       </c>
-      <c r="P28" s="4" t="s">
+      <c r="P28" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="Q28" s="4" t="s">
+      <c r="Q28" s="6" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="29" ht="54.75" spans="1:18">
+    <row r="29" ht="63.5" customHeight="1" spans="1:18">
       <c r="A29" s="5" t="s">
         <v>329</v>
       </c>
@@ -8631,7 +9116,7 @@
         <v>331</v>
       </c>
       <c r="D29" s="5"/>
-      <c r="E29" s="9">
+      <c r="E29" s="10">
         <v>52213</v>
       </c>
       <c r="F29" s="7" t="s">
@@ -8640,37 +9125,39 @@
       <c r="G29" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="H29" s="5"/>
-      <c r="I29" s="10" t="s">
+      <c r="H29" s="8">
+        <v>46193</v>
+      </c>
+      <c r="I29" s="5" t="s">
         <v>255</v>
       </c>
-      <c r="J29" t="s">
+      <c r="J29" s="9" t="s">
         <v>333</v>
       </c>
-      <c r="K29" s="4" t="s">
+      <c r="K29" s="5" t="s">
         <v>334</v>
       </c>
-      <c r="L29" s="4" t="s">
+      <c r="L29" s="6" t="s">
         <v>335</v>
       </c>
-      <c r="M29" s="4" t="s">
+      <c r="M29" s="5" t="s">
         <v>336</v>
       </c>
-      <c r="N29" s="4" t="s">
+      <c r="N29" s="6" t="s">
         <v>337</v>
       </c>
-      <c r="O29" s="4" t="s">
+      <c r="O29" s="6" t="s">
         <v>338</v>
       </c>
-      <c r="P29" t="s">
+      <c r="P29" s="9" t="s">
         <v>339</v>
       </c>
-      <c r="Q29" s="12" t="s">
+      <c r="Q29" s="6" t="s">
         <v>340</v>
       </c>
       <c r="R29" s="4"/>
     </row>
-    <row r="30" ht="54.75" spans="1:18">
+    <row r="30" ht="63.5" customHeight="1" spans="1:18">
       <c r="A30" s="5" t="s">
         <v>341</v>
       </c>
@@ -8690,37 +9177,39 @@
       <c r="G30" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="H30" s="14"/>
-      <c r="I30" s="10" t="s">
+      <c r="H30" s="8">
+        <v>46193</v>
+      </c>
+      <c r="I30" s="5" t="s">
         <v>276</v>
       </c>
-      <c r="J30" t="s">
+      <c r="J30" s="9" t="s">
         <v>333</v>
       </c>
-      <c r="K30" s="4" t="s">
+      <c r="K30" s="5" t="s">
         <v>344</v>
       </c>
-      <c r="L30" s="4" t="s">
+      <c r="L30" s="6" t="s">
         <v>345</v>
       </c>
-      <c r="M30" s="4" t="s">
+      <c r="M30" s="5" t="s">
         <v>346</v>
       </c>
-      <c r="N30" s="4" t="s">
+      <c r="N30" s="6" t="s">
         <v>347</v>
       </c>
-      <c r="O30" s="4" t="s">
+      <c r="O30" s="6" t="s">
         <v>348</v>
       </c>
-      <c r="P30" t="s">
+      <c r="P30" s="9" t="s">
         <v>342</v>
       </c>
-      <c r="Q30" s="12" t="s">
+      <c r="Q30" s="6" t="s">
         <v>349</v>
       </c>
       <c r="R30" s="4"/>
     </row>
-    <row r="31" ht="54.75" spans="1:18">
+    <row r="31" ht="63.5" customHeight="1" spans="1:18">
       <c r="A31" s="5" t="s">
         <v>350</v>
       </c>
@@ -8740,37 +9229,39 @@
       <c r="G31" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="H31" s="14"/>
-      <c r="I31" t="s">
+      <c r="H31" s="8">
+        <v>46193</v>
+      </c>
+      <c r="I31" s="9" t="s">
         <v>287</v>
       </c>
-      <c r="J31" t="s">
+      <c r="J31" s="9" t="s">
         <v>333</v>
       </c>
-      <c r="K31" s="4" t="s">
+      <c r="K31" s="5" t="s">
         <v>353</v>
       </c>
-      <c r="L31" s="4" t="s">
+      <c r="L31" s="6" t="s">
         <v>354</v>
       </c>
-      <c r="M31" s="4" t="s">
+      <c r="M31" s="5" t="s">
         <v>355</v>
       </c>
-      <c r="N31" s="4" t="s">
+      <c r="N31" s="6" t="s">
         <v>356</v>
       </c>
-      <c r="O31" s="4" t="s">
+      <c r="O31" s="6" t="s">
         <v>357</v>
       </c>
-      <c r="P31" t="s">
+      <c r="P31" s="9" t="s">
         <v>358</v>
       </c>
-      <c r="Q31" s="12" t="s">
+      <c r="Q31" s="6" t="s">
         <v>359</v>
       </c>
       <c r="R31" s="4"/>
     </row>
-    <row r="32" ht="54.75" spans="1:18">
+    <row r="32" ht="63.5" customHeight="1" spans="1:18">
       <c r="A32" s="5" t="s">
         <v>360</v>
       </c>
@@ -8790,37 +9281,39 @@
       <c r="G32" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="H32" s="15"/>
-      <c r="I32" t="s">
+      <c r="H32" s="8">
+        <v>46191</v>
+      </c>
+      <c r="I32" s="9" t="s">
         <v>299</v>
       </c>
-      <c r="J32" t="s">
+      <c r="J32" s="9" t="s">
         <v>333</v>
       </c>
-      <c r="K32" s="4" t="s">
+      <c r="K32" s="5" t="s">
         <v>363</v>
       </c>
-      <c r="L32" s="4" t="s">
+      <c r="L32" s="6" t="s">
         <v>364</v>
       </c>
-      <c r="M32" s="4" t="s">
+      <c r="M32" s="5" t="s">
         <v>365</v>
       </c>
-      <c r="N32" s="4" t="s">
+      <c r="N32" s="6" t="s">
         <v>366</v>
       </c>
-      <c r="O32" s="4" t="s">
+      <c r="O32" s="6" t="s">
         <v>367</v>
       </c>
-      <c r="P32" t="s">
+      <c r="P32" s="9" t="s">
         <v>368</v>
       </c>
-      <c r="Q32" s="12" t="s">
+      <c r="Q32" s="6" t="s">
         <v>369</v>
       </c>
       <c r="R32" s="4"/>
     </row>
-    <row r="33" ht="54" spans="1:18">
+    <row r="33" ht="63.5" customHeight="1" spans="1:18">
       <c r="A33" s="5" t="s">
         <v>370</v>
       </c>
@@ -8840,37 +9333,39 @@
       <c r="G33" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="H33" s="5"/>
-      <c r="I33" t="s">
+      <c r="H33" s="8">
+        <v>46191</v>
+      </c>
+      <c r="I33" s="9" t="s">
         <v>373</v>
       </c>
-      <c r="J33" t="s">
+      <c r="J33" s="9" t="s">
         <v>333</v>
       </c>
-      <c r="K33" s="4" t="s">
+      <c r="K33" s="5" t="s">
         <v>374</v>
       </c>
-      <c r="L33" s="4" t="s">
+      <c r="L33" s="6" t="s">
         <v>375</v>
       </c>
-      <c r="M33" s="4" t="s">
+      <c r="M33" s="5" t="s">
         <v>376</v>
       </c>
-      <c r="N33" s="4" t="s">
+      <c r="N33" s="6" t="s">
         <v>377</v>
       </c>
-      <c r="O33" s="4" t="s">
+      <c r="O33" s="6" t="s">
         <v>378</v>
       </c>
-      <c r="P33" t="s">
+      <c r="P33" s="9" t="s">
         <v>379</v>
       </c>
-      <c r="Q33" s="12" t="s">
+      <c r="Q33" s="6" t="s">
         <v>380</v>
       </c>
       <c r="R33" s="4"/>
     </row>
-    <row r="34" ht="54" spans="1:18">
+    <row r="34" ht="63.5" customHeight="1" spans="1:18">
       <c r="A34" s="5" t="s">
         <v>381</v>
       </c>
@@ -8890,37 +9385,39 @@
       <c r="G34" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="H34" s="5"/>
-      <c r="I34" t="s">
+      <c r="H34" s="8">
+        <v>46191</v>
+      </c>
+      <c r="I34" s="9" t="s">
         <v>384</v>
       </c>
-      <c r="J34" t="s">
+      <c r="J34" s="9" t="s">
         <v>333</v>
       </c>
-      <c r="K34" s="4" t="s">
+      <c r="K34" s="5" t="s">
         <v>385</v>
       </c>
-      <c r="L34" s="4" t="s">
+      <c r="L34" s="6" t="s">
         <v>386</v>
       </c>
-      <c r="M34" s="4" t="s">
+      <c r="M34" s="5" t="s">
         <v>387</v>
       </c>
-      <c r="N34" s="4" t="s">
+      <c r="N34" s="6" t="s">
         <v>388</v>
       </c>
-      <c r="O34" s="4" t="s">
+      <c r="O34" s="6" t="s">
         <v>389</v>
       </c>
-      <c r="P34" t="s">
+      <c r="P34" s="9" t="s">
         <v>390</v>
       </c>
-      <c r="Q34" s="12" t="s">
+      <c r="Q34" s="6" t="s">
         <v>391</v>
       </c>
       <c r="R34" s="4"/>
     </row>
-    <row r="35" ht="81" spans="1:18">
+    <row r="35" ht="96.5" customHeight="1" spans="1:18">
       <c r="A35" s="5" t="s">
         <v>392</v>
       </c>
@@ -8940,20 +9437,22 @@
       <c r="G35" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="H35" s="5"/>
-      <c r="I35" s="16" t="s">
+      <c r="H35" s="15">
+        <v>46194</v>
+      </c>
+      <c r="I35" s="9" t="s">
         <v>395</v>
       </c>
-      <c r="J35" t="s">
+      <c r="J35" s="9" t="s">
         <v>333</v>
       </c>
-      <c r="K35" s="16" t="s">
+      <c r="K35" s="9" t="s">
         <v>396</v>
       </c>
       <c r="L35" s="16" t="s">
         <v>397</v>
       </c>
-      <c r="M35" s="16" t="s">
+      <c r="M35" s="9" t="s">
         <v>398</v>
       </c>
       <c r="N35" s="16" t="s">
@@ -8962,7 +9461,7 @@
       <c r="O35" s="16" t="s">
         <v>400</v>
       </c>
-      <c r="P35" s="16" t="s">
+      <c r="P35" s="9" t="s">
         <v>401</v>
       </c>
       <c r="Q35" s="16" t="s">
@@ -8970,7 +9469,7 @@
       </c>
       <c r="R35" s="4"/>
     </row>
-    <row r="36" ht="81" spans="1:18">
+    <row r="36" ht="96.5" customHeight="1" spans="1:18">
       <c r="A36" s="5" t="s">
         <v>403</v>
       </c>
@@ -8990,20 +9489,22 @@
       <c r="G36" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="H36" s="5"/>
-      <c r="I36" s="17" t="s">
+      <c r="H36" s="15">
+        <v>46194</v>
+      </c>
+      <c r="I36" s="9" t="s">
         <v>406</v>
       </c>
-      <c r="J36" t="s">
+      <c r="J36" s="9" t="s">
         <v>333</v>
       </c>
-      <c r="K36" s="16" t="s">
+      <c r="K36" s="9" t="s">
         <v>407</v>
       </c>
       <c r="L36" s="16" t="s">
         <v>408</v>
       </c>
-      <c r="M36" s="16" t="s">
+      <c r="M36" s="9" t="s">
         <v>409</v>
       </c>
       <c r="N36" s="16" t="s">
@@ -9012,7 +9513,7 @@
       <c r="O36" s="16" t="s">
         <v>411</v>
       </c>
-      <c r="P36" s="16" t="s">
+      <c r="P36" s="9" t="s">
         <v>412</v>
       </c>
       <c r="Q36" s="16" t="s">
@@ -9020,7 +9521,7 @@
       </c>
       <c r="R36" s="4"/>
     </row>
-    <row r="37" ht="81" spans="1:18">
+    <row r="37" ht="96.5" customHeight="1" spans="1:18">
       <c r="A37" s="5" t="s">
         <v>414</v>
       </c>
@@ -9031,7 +9532,7 @@
         <v>19</v>
       </c>
       <c r="D37" s="5"/>
-      <c r="E37" s="9">
+      <c r="E37" s="10">
         <v>52496</v>
       </c>
       <c r="F37" s="7" t="s">
@@ -9040,20 +9541,22 @@
       <c r="G37" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="H37" s="5"/>
-      <c r="I37" s="16" t="s">
+      <c r="H37" s="8">
+        <v>46193</v>
+      </c>
+      <c r="I37" s="9" t="s">
         <v>417</v>
       </c>
-      <c r="J37" t="s">
+      <c r="J37" s="9" t="s">
         <v>333</v>
       </c>
-      <c r="K37" s="16" t="s">
+      <c r="K37" s="9" t="s">
         <v>418</v>
       </c>
       <c r="L37" s="16" t="s">
         <v>419</v>
       </c>
-      <c r="M37" s="16" t="s">
+      <c r="M37" s="9" t="s">
         <v>420</v>
       </c>
       <c r="N37" s="16" t="s">
@@ -9062,7 +9565,7 @@
       <c r="O37" s="16" t="s">
         <v>422</v>
       </c>
-      <c r="P37" s="16" t="s">
+      <c r="P37" s="9" t="s">
         <v>423</v>
       </c>
       <c r="Q37" s="16" t="s">
@@ -9070,7 +9573,7 @@
       </c>
       <c r="R37" s="4"/>
     </row>
-    <row r="38" ht="81" spans="1:18">
+    <row r="38" ht="96.5" customHeight="1" spans="1:18">
       <c r="A38" s="5" t="s">
         <v>425</v>
       </c>
@@ -9081,7 +9584,7 @@
         <v>19</v>
       </c>
       <c r="D38" s="5"/>
-      <c r="E38" s="9">
+      <c r="E38" s="10">
         <v>52494</v>
       </c>
       <c r="F38" s="7" t="s">
@@ -9090,20 +9593,22 @@
       <c r="G38" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="H38" s="5"/>
-      <c r="I38" s="16" t="s">
+      <c r="H38" s="8">
+        <v>46193</v>
+      </c>
+      <c r="I38" s="9" t="s">
         <v>428</v>
       </c>
-      <c r="J38" t="s">
+      <c r="J38" s="9" t="s">
         <v>333</v>
       </c>
-      <c r="K38" s="16" t="s">
+      <c r="K38" s="9" t="s">
         <v>429</v>
       </c>
       <c r="L38" s="16" t="s">
         <v>430</v>
       </c>
-      <c r="M38" s="16" t="s">
+      <c r="M38" s="9" t="s">
         <v>431</v>
       </c>
       <c r="N38" s="16" t="s">
@@ -9112,14 +9617,14 @@
       <c r="O38" s="16" t="s">
         <v>433</v>
       </c>
-      <c r="P38" s="16" t="s">
+      <c r="P38" s="9" t="s">
         <v>434</v>
       </c>
       <c r="Q38" s="16" t="s">
         <v>435</v>
       </c>
     </row>
-    <row r="39" ht="68.25" spans="1:18">
+    <row r="39" ht="80" customHeight="1" spans="1:18">
       <c r="A39" s="5" t="s">
         <v>436</v>
       </c>
@@ -9130,7 +9635,7 @@
         <v>19</v>
       </c>
       <c r="D39" s="5"/>
-      <c r="E39" s="9">
+      <c r="E39" s="10">
         <v>52497</v>
       </c>
       <c r="F39" s="7" t="s">
@@ -9139,20 +9644,22 @@
       <c r="G39" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="H39" s="5"/>
-      <c r="I39" s="16" t="s">
+      <c r="H39" s="8">
+        <v>46193</v>
+      </c>
+      <c r="I39" s="9" t="s">
         <v>439</v>
       </c>
-      <c r="J39" t="s">
+      <c r="J39" s="9" t="s">
         <v>333</v>
       </c>
-      <c r="K39" s="16" t="s">
+      <c r="K39" s="9" t="s">
         <v>440</v>
       </c>
       <c r="L39" s="16" t="s">
         <v>441</v>
       </c>
-      <c r="M39" s="16" t="s">
+      <c r="M39" s="9" t="s">
         <v>442</v>
       </c>
       <c r="N39" s="16" t="s">
@@ -9161,14 +9668,14 @@
       <c r="O39" s="16" t="s">
         <v>444</v>
       </c>
-      <c r="P39" s="16" t="s">
+      <c r="P39" s="9" t="s">
         <v>445</v>
       </c>
       <c r="Q39" s="16" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="40" ht="68.25" spans="1:18">
+    <row r="40" ht="96.5" customHeight="1" spans="1:18">
       <c r="A40" s="5" t="s">
         <v>447</v>
       </c>
@@ -9179,29 +9686,31 @@
         <v>19</v>
       </c>
       <c r="D40" s="5"/>
-      <c r="E40" s="9">
+      <c r="E40" s="10">
         <v>52500</v>
       </c>
-      <c r="F40" s="18" t="s">
+      <c r="F40" s="17" t="s">
         <v>449</v>
       </c>
       <c r="G40" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="H40" s="19"/>
-      <c r="I40" s="16" t="s">
+      <c r="H40" s="8">
+        <v>46191</v>
+      </c>
+      <c r="I40" s="9" t="s">
         <v>450</v>
       </c>
-      <c r="J40" t="s">
+      <c r="J40" s="9" t="s">
         <v>333</v>
       </c>
-      <c r="K40" s="16" t="s">
+      <c r="K40" s="9" t="s">
         <v>451</v>
       </c>
       <c r="L40" s="16" t="s">
         <v>452</v>
       </c>
-      <c r="M40" s="16" t="s">
+      <c r="M40" s="9" t="s">
         <v>453</v>
       </c>
       <c r="N40" s="16" t="s">
@@ -9210,14 +9719,14 @@
       <c r="O40" s="16" t="s">
         <v>455</v>
       </c>
-      <c r="P40" s="16" t="s">
+      <c r="P40" s="9" t="s">
         <v>456</v>
       </c>
       <c r="Q40" s="16" t="s">
         <v>457</v>
       </c>
     </row>
-    <row r="41" ht="68.25" spans="1:18">
+    <row r="41" ht="96.5" customHeight="1" spans="1:18">
       <c r="A41" s="5" t="s">
         <v>458</v>
       </c>
@@ -9228,29 +9737,31 @@
         <v>19</v>
       </c>
       <c r="D41" s="5"/>
-      <c r="E41" s="9">
+      <c r="E41" s="10">
         <v>52495</v>
       </c>
-      <c r="F41" s="18" t="s">
+      <c r="F41" s="17" t="s">
         <v>460</v>
       </c>
       <c r="G41" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="H41" s="19"/>
-      <c r="I41" s="16" t="s">
+      <c r="H41" s="8">
+        <v>46191</v>
+      </c>
+      <c r="I41" s="9" t="s">
         <v>461</v>
       </c>
-      <c r="J41" t="s">
+      <c r="J41" s="9" t="s">
         <v>333</v>
       </c>
-      <c r="K41" s="16" t="s">
+      <c r="K41" s="9" t="s">
         <v>462</v>
       </c>
       <c r="L41" s="16" t="s">
         <v>463</v>
       </c>
-      <c r="M41" s="16" t="s">
+      <c r="M41" s="9" t="s">
         <v>464</v>
       </c>
       <c r="N41" s="16" t="s">
@@ -9259,14 +9770,14 @@
       <c r="O41" s="16" t="s">
         <v>466</v>
       </c>
-      <c r="P41" s="16" t="s">
+      <c r="P41" s="9" t="s">
         <v>467</v>
       </c>
       <c r="Q41" s="16" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="42" ht="68.25" spans="1:18">
+    <row r="42" ht="80" customHeight="1" spans="1:18">
       <c r="A42" s="5" t="s">
         <v>469</v>
       </c>
@@ -9277,29 +9788,31 @@
         <v>19</v>
       </c>
       <c r="D42" s="5"/>
-      <c r="E42" s="9">
+      <c r="E42" s="10">
         <v>52498</v>
       </c>
-      <c r="F42" s="18" t="s">
+      <c r="F42" s="17" t="s">
         <v>471</v>
       </c>
       <c r="G42" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="H42" s="19"/>
-      <c r="I42" s="16" t="s">
+      <c r="H42" s="8">
+        <v>46191</v>
+      </c>
+      <c r="I42" s="9" t="s">
         <v>472</v>
       </c>
-      <c r="J42" t="s">
+      <c r="J42" s="9" t="s">
         <v>333</v>
       </c>
-      <c r="K42" s="16" t="s">
+      <c r="K42" s="9" t="s">
         <v>473</v>
       </c>
       <c r="L42" s="16" t="s">
         <v>474</v>
       </c>
-      <c r="M42" s="16" t="s">
+      <c r="M42" s="9" t="s">
         <v>475</v>
       </c>
       <c r="N42" s="16" t="s">
@@ -9308,91 +9821,975 @@
       <c r="O42" s="16" t="s">
         <v>477</v>
       </c>
-      <c r="P42" s="16" t="s">
+      <c r="P42" s="9" t="s">
         <v>478</v>
       </c>
       <c r="Q42" s="16" t="s">
         <v>479</v>
       </c>
     </row>
-    <row r="43" ht="16.5" spans="1:18">
-      <c r="F43" s="20"/>
-      <c r="G43" s="5"/>
+    <row r="43" ht="63.5" customHeight="1" spans="1:18">
+      <c r="A43" s="9" t="s">
+        <v>480</v>
+      </c>
+      <c r="B43" s="16" t="s">
+        <v>481</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="D43" s="13"/>
+      <c r="E43" s="18">
+        <v>54850</v>
+      </c>
+      <c r="F43" s="34" t="s">
+        <v>482</v>
+      </c>
+      <c r="G43" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H43" s="15">
+        <v>46194</v>
+      </c>
+      <c r="I43" s="9" t="s">
+        <v>483</v>
+      </c>
+      <c r="J43" s="9" t="s">
+        <v>333</v>
+      </c>
+      <c r="K43" s="9" t="s">
+        <v>484</v>
+      </c>
+      <c r="L43" s="16" t="s">
+        <v>485</v>
+      </c>
+      <c r="M43" s="9" t="s">
+        <v>486</v>
+      </c>
+      <c r="N43" s="16" t="s">
+        <v>487</v>
+      </c>
+      <c r="O43" s="16" t="s">
+        <v>488</v>
+      </c>
+      <c r="P43" s="9" t="s">
+        <v>489</v>
+      </c>
+      <c r="Q43" s="16" t="s">
+        <v>490</v>
+      </c>
     </row>
-    <row r="44" ht="16.5" spans="1:18">
-      <c r="F44" s="20"/>
-      <c r="G44" s="5"/>
+    <row r="44" ht="63.5" customHeight="1" spans="1:18">
+      <c r="A44" s="9" t="s">
+        <v>491</v>
+      </c>
+      <c r="B44" s="16" t="s">
+        <v>492</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="D44" s="13"/>
+      <c r="E44" s="18">
+        <v>54849</v>
+      </c>
+      <c r="F44" s="34" t="s">
+        <v>493</v>
+      </c>
+      <c r="G44" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H44" s="15">
+        <v>46194</v>
+      </c>
+      <c r="I44" s="20" t="s">
+        <v>494</v>
+      </c>
+      <c r="J44" s="9" t="s">
+        <v>333</v>
+      </c>
+      <c r="K44" s="9" t="s">
+        <v>495</v>
+      </c>
+      <c r="L44" s="16" t="s">
+        <v>496</v>
+      </c>
+      <c r="M44" s="9" t="s">
+        <v>497</v>
+      </c>
+      <c r="N44" s="16" t="s">
+        <v>498</v>
+      </c>
+      <c r="O44" s="16" t="s">
+        <v>499</v>
+      </c>
+      <c r="P44" s="9" t="s">
+        <v>500</v>
+      </c>
+      <c r="Q44" s="16" t="s">
+        <v>501</v>
+      </c>
     </row>
-    <row r="45" ht="16.5" spans="1:18">
-      <c r="F45" s="20"/>
-      <c r="G45" s="5"/>
+    <row r="45" ht="63.5" customHeight="1" spans="1:18">
+      <c r="A45" s="9" t="s">
+        <v>502</v>
+      </c>
+      <c r="B45" s="16" t="s">
+        <v>503</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="D45" s="13"/>
+      <c r="E45" s="18">
+        <v>54855</v>
+      </c>
+      <c r="F45" s="14" t="s">
+        <v>504</v>
+      </c>
+      <c r="G45" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="H45" s="15">
+        <v>46194</v>
+      </c>
+      <c r="I45" s="9" t="s">
+        <v>505</v>
+      </c>
+      <c r="J45" s="9" t="s">
+        <v>333</v>
+      </c>
+      <c r="K45" s="9" t="s">
+        <v>506</v>
+      </c>
+      <c r="L45" s="16" t="s">
+        <v>507</v>
+      </c>
+      <c r="M45" s="9" t="s">
+        <v>508</v>
+      </c>
+      <c r="N45" s="16" t="s">
+        <v>509</v>
+      </c>
+      <c r="O45" s="16" t="s">
+        <v>510</v>
+      </c>
+      <c r="P45" s="9" t="s">
+        <v>511</v>
+      </c>
+      <c r="Q45" s="16" t="s">
+        <v>512</v>
+      </c>
     </row>
-    <row r="46" ht="16.5" spans="1:18">
-      <c r="F46" s="20"/>
-      <c r="G46" s="5"/>
+    <row r="46" ht="63.5" customHeight="1" spans="1:18">
+      <c r="A46" s="9" t="s">
+        <v>513</v>
+      </c>
+      <c r="B46" s="16" t="s">
+        <v>514</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="D46" s="13"/>
+      <c r="E46" s="18">
+        <v>54853</v>
+      </c>
+      <c r="F46" s="14" t="s">
+        <v>515</v>
+      </c>
+      <c r="G46" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H46" s="13"/>
+      <c r="I46" s="9" t="s">
+        <v>516</v>
+      </c>
+      <c r="J46" s="9"/>
+      <c r="K46" s="9" t="s">
+        <v>517</v>
+      </c>
+      <c r="L46" s="16" t="s">
+        <v>518</v>
+      </c>
+      <c r="M46" s="9" t="s">
+        <v>519</v>
+      </c>
+      <c r="N46" s="16" t="s">
+        <v>520</v>
+      </c>
+      <c r="O46" s="16" t="s">
+        <v>521</v>
+      </c>
+      <c r="P46" s="9" t="s">
+        <v>522</v>
+      </c>
+      <c r="Q46" s="16" t="s">
+        <v>523</v>
+      </c>
     </row>
-    <row r="47" ht="13.5" spans="1:18">
-      <c r="F47" s="20"/>
+    <row r="47" ht="63.5" customHeight="1" spans="1:18">
+      <c r="A47" s="9" t="s">
+        <v>524</v>
+      </c>
+      <c r="B47" s="16" t="s">
+        <v>525</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="D47" s="13"/>
+      <c r="E47" s="13">
+        <v>54848</v>
+      </c>
+      <c r="F47" s="14" t="s">
+        <v>526</v>
+      </c>
+      <c r="G47" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="H47" s="13"/>
+      <c r="I47" s="9" t="s">
+        <v>527</v>
+      </c>
+      <c r="J47" s="13"/>
+      <c r="K47" s="9" t="s">
+        <v>528</v>
+      </c>
+      <c r="L47" s="16" t="s">
+        <v>529</v>
+      </c>
+      <c r="M47" s="9" t="s">
+        <v>530</v>
+      </c>
+      <c r="N47" s="16" t="s">
+        <v>531</v>
+      </c>
+      <c r="O47" s="16" t="s">
+        <v>532</v>
+      </c>
+      <c r="P47" s="9" t="s">
+        <v>533</v>
+      </c>
+      <c r="Q47" s="16" t="s">
+        <v>534</v>
+      </c>
     </row>
-    <row r="48" spans="1:18">
-      <c r="F48" s="20"/>
+    <row r="48" ht="63.5" customHeight="1" spans="1:18">
+      <c r="A48" s="9" t="s">
+        <v>535</v>
+      </c>
+      <c r="B48" s="16" t="s">
+        <v>536</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="D48" s="13"/>
+      <c r="E48" s="18">
+        <v>54847</v>
+      </c>
+      <c r="F48" s="14" t="s">
+        <v>537</v>
+      </c>
+      <c r="G48" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="H48" s="13"/>
+      <c r="I48" s="9" t="s">
+        <v>538</v>
+      </c>
+      <c r="J48" s="13"/>
+      <c r="K48" s="9" t="s">
+        <v>539</v>
+      </c>
+      <c r="L48" s="16" t="s">
+        <v>540</v>
+      </c>
+      <c r="M48" s="9" t="s">
+        <v>541</v>
+      </c>
+      <c r="N48" s="16" t="s">
+        <v>542</v>
+      </c>
+      <c r="O48" s="16" t="s">
+        <v>543</v>
+      </c>
+      <c r="P48" s="9" t="s">
+        <v>544</v>
+      </c>
+      <c r="Q48" s="16" t="s">
+        <v>545</v>
+      </c>
     </row>
-    <row r="49" spans="6:6">
-      <c r="F49" s="20"/>
+    <row r="49" ht="63.5" customHeight="1" spans="1:17">
+      <c r="A49" s="9" t="s">
+        <v>546</v>
+      </c>
+      <c r="B49" s="16" t="s">
+        <v>547</v>
+      </c>
+      <c r="C49" s="9" t="s">
+        <v>548</v>
+      </c>
+      <c r="D49" s="13"/>
+      <c r="E49" s="18">
+        <v>54862</v>
+      </c>
+      <c r="F49" s="14" t="s">
+        <v>549</v>
+      </c>
+      <c r="G49" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="H49" s="15">
+        <v>46194</v>
+      </c>
+      <c r="I49" s="9" t="s">
+        <v>550</v>
+      </c>
+      <c r="J49" s="9" t="s">
+        <v>333</v>
+      </c>
+      <c r="K49" s="9" t="s">
+        <v>551</v>
+      </c>
+      <c r="L49" s="16" t="s">
+        <v>552</v>
+      </c>
+      <c r="M49" s="9" t="s">
+        <v>553</v>
+      </c>
+      <c r="N49" s="16" t="s">
+        <v>554</v>
+      </c>
+      <c r="O49" s="16" t="s">
+        <v>555</v>
+      </c>
+      <c r="P49" s="9" t="s">
+        <v>556</v>
+      </c>
+      <c r="Q49" s="16" t="s">
+        <v>557</v>
+      </c>
     </row>
-    <row r="50" spans="6:6">
-      <c r="F50" s="20"/>
+    <row r="50" ht="63.5" customHeight="1" spans="1:17">
+      <c r="A50" s="9" t="s">
+        <v>558</v>
+      </c>
+      <c r="B50" s="16" t="s">
+        <v>559</v>
+      </c>
+      <c r="C50" s="9" t="s">
+        <v>548</v>
+      </c>
+      <c r="D50" s="13"/>
+      <c r="E50" s="18">
+        <v>54858</v>
+      </c>
+      <c r="F50" s="14" t="s">
+        <v>560</v>
+      </c>
+      <c r="G50" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H50" s="15">
+        <v>46194</v>
+      </c>
+      <c r="I50" s="9" t="s">
+        <v>561</v>
+      </c>
+      <c r="J50" s="9" t="s">
+        <v>333</v>
+      </c>
+      <c r="K50" s="9" t="s">
+        <v>562</v>
+      </c>
+      <c r="L50" s="16" t="s">
+        <v>563</v>
+      </c>
+      <c r="M50" s="9" t="s">
+        <v>564</v>
+      </c>
+      <c r="N50" s="16" t="s">
+        <v>565</v>
+      </c>
+      <c r="O50" s="16" t="s">
+        <v>566</v>
+      </c>
+      <c r="P50" s="9" t="s">
+        <v>567</v>
+      </c>
+      <c r="Q50" s="16" t="s">
+        <v>568</v>
+      </c>
     </row>
-    <row r="51" spans="6:6">
-      <c r="F51" s="20"/>
+    <row r="51" ht="63.5" customHeight="1" spans="1:17">
+      <c r="A51" s="9" t="s">
+        <v>569</v>
+      </c>
+      <c r="B51" s="16" t="s">
+        <v>570</v>
+      </c>
+      <c r="C51" s="9" t="s">
+        <v>548</v>
+      </c>
+      <c r="D51" s="13"/>
+      <c r="E51" s="18">
+        <v>54859</v>
+      </c>
+      <c r="F51" s="14" t="s">
+        <v>571</v>
+      </c>
+      <c r="G51" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="H51" s="15">
+        <v>46194</v>
+      </c>
+      <c r="I51" s="9" t="s">
+        <v>572</v>
+      </c>
+      <c r="J51" s="9" t="s">
+        <v>333</v>
+      </c>
+      <c r="K51" s="9" t="s">
+        <v>573</v>
+      </c>
+      <c r="L51" s="16" t="s">
+        <v>574</v>
+      </c>
+      <c r="M51" s="9" t="s">
+        <v>575</v>
+      </c>
+      <c r="N51" s="16" t="s">
+        <v>576</v>
+      </c>
+      <c r="O51" s="16" t="s">
+        <v>577</v>
+      </c>
+      <c r="P51" s="9" t="s">
+        <v>578</v>
+      </c>
+      <c r="Q51" s="16" t="s">
+        <v>579</v>
+      </c>
     </row>
-    <row r="52" spans="6:6">
-      <c r="F52" s="20"/>
+    <row r="52" ht="63.5" customHeight="1" spans="1:17">
+      <c r="A52" s="9" t="s">
+        <v>580</v>
+      </c>
+      <c r="B52" s="16" t="s">
+        <v>581</v>
+      </c>
+      <c r="C52" s="9" t="s">
+        <v>548</v>
+      </c>
+      <c r="D52" s="13"/>
+      <c r="E52" s="13">
+        <v>54865</v>
+      </c>
+      <c r="F52" s="14" t="s">
+        <v>582</v>
+      </c>
+      <c r="G52" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H52" s="13"/>
+      <c r="I52" s="9" t="s">
+        <v>583</v>
+      </c>
+      <c r="J52" s="13"/>
+      <c r="K52" s="9" t="s">
+        <v>584</v>
+      </c>
+      <c r="L52" s="16" t="s">
+        <v>585</v>
+      </c>
+      <c r="M52" s="9" t="s">
+        <v>586</v>
+      </c>
+      <c r="N52" s="16" t="s">
+        <v>587</v>
+      </c>
+      <c r="O52" s="16" t="s">
+        <v>588</v>
+      </c>
+      <c r="P52" s="9" t="s">
+        <v>589</v>
+      </c>
+      <c r="Q52" s="16" t="s">
+        <v>590</v>
+      </c>
     </row>
-    <row r="53" spans="6:6">
-      <c r="F53" s="20"/>
+    <row r="53" ht="63.5" customHeight="1" spans="1:17">
+      <c r="A53" s="9" t="s">
+        <v>591</v>
+      </c>
+      <c r="B53" s="16" t="s">
+        <v>592</v>
+      </c>
+      <c r="C53" s="9" t="s">
+        <v>548</v>
+      </c>
+      <c r="D53" s="13"/>
+      <c r="E53" s="18">
+        <v>54864</v>
+      </c>
+      <c r="F53" s="14" t="s">
+        <v>593</v>
+      </c>
+      <c r="G53" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H53" s="13"/>
+      <c r="I53" s="9" t="s">
+        <v>594</v>
+      </c>
+      <c r="J53" s="13"/>
+      <c r="K53" s="9" t="s">
+        <v>595</v>
+      </c>
+      <c r="L53" s="16" t="s">
+        <v>596</v>
+      </c>
+      <c r="M53" s="9" t="s">
+        <v>597</v>
+      </c>
+      <c r="N53" s="16" t="s">
+        <v>598</v>
+      </c>
+      <c r="O53" s="16" t="s">
+        <v>599</v>
+      </c>
+      <c r="P53" s="9" t="s">
+        <v>600</v>
+      </c>
+      <c r="Q53" s="16" t="s">
+        <v>601</v>
+      </c>
     </row>
-    <row r="54" spans="6:6">
-      <c r="F54" s="20"/>
+    <row r="54" ht="63.5" customHeight="1" spans="1:17">
+      <c r="A54" s="9" t="s">
+        <v>602</v>
+      </c>
+      <c r="B54" s="16" t="s">
+        <v>603</v>
+      </c>
+      <c r="C54" s="9" t="s">
+        <v>548</v>
+      </c>
+      <c r="D54" s="13"/>
+      <c r="E54" s="18">
+        <v>54863</v>
+      </c>
+      <c r="F54" s="14" t="s">
+        <v>604</v>
+      </c>
+      <c r="G54" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="H54" s="13"/>
+      <c r="I54" s="9" t="s">
+        <v>605</v>
+      </c>
+      <c r="J54" s="13"/>
+      <c r="K54" s="9" t="s">
+        <v>606</v>
+      </c>
+      <c r="L54" s="16" t="s">
+        <v>607</v>
+      </c>
+      <c r="M54" s="9" t="s">
+        <v>608</v>
+      </c>
+      <c r="N54" s="16" t="s">
+        <v>609</v>
+      </c>
+      <c r="O54" s="16" t="s">
+        <v>610</v>
+      </c>
+      <c r="P54" s="9" t="s">
+        <v>611</v>
+      </c>
+      <c r="Q54" s="16" t="s">
+        <v>612</v>
+      </c>
     </row>
-    <row r="55" spans="6:6">
-      <c r="F55" s="20"/>
+    <row r="55" ht="63.5" customHeight="1" spans="1:17">
+      <c r="A55" s="9" t="s">
+        <v>613</v>
+      </c>
+      <c r="B55" s="16" t="s">
+        <v>614</v>
+      </c>
+      <c r="C55" s="9" t="s">
+        <v>548</v>
+      </c>
+      <c r="D55" s="13"/>
+      <c r="E55" s="18">
+        <v>54857</v>
+      </c>
+      <c r="F55" s="14" t="s">
+        <v>615</v>
+      </c>
+      <c r="G55" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H55" s="13"/>
+      <c r="I55" s="9" t="s">
+        <v>616</v>
+      </c>
+      <c r="J55" s="13"/>
+      <c r="K55" s="9" t="s">
+        <v>617</v>
+      </c>
+      <c r="L55" s="16" t="s">
+        <v>618</v>
+      </c>
+      <c r="M55" s="9" t="s">
+        <v>619</v>
+      </c>
+      <c r="N55" s="16" t="s">
+        <v>620</v>
+      </c>
+      <c r="O55" s="16" t="s">
+        <v>621</v>
+      </c>
+      <c r="P55" s="9" t="s">
+        <v>622</v>
+      </c>
+      <c r="Q55" s="16" t="s">
+        <v>623</v>
+      </c>
     </row>
-    <row r="56" spans="6:6">
-      <c r="F56" s="20"/>
+    <row r="56" ht="47" customHeight="1" spans="1:17">
+      <c r="A56" s="9" t="s">
+        <v>624</v>
+      </c>
+      <c r="B56" s="16" t="s">
+        <v>625</v>
+      </c>
+      <c r="C56" s="9" t="s">
+        <v>548</v>
+      </c>
+      <c r="D56" s="13"/>
+      <c r="E56" s="18">
+        <v>54856</v>
+      </c>
+      <c r="F56" s="14"/>
+      <c r="G56" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="H56" s="13"/>
+      <c r="I56" s="9" t="s">
+        <v>626</v>
+      </c>
+      <c r="J56" s="13"/>
+      <c r="K56" s="9" t="s">
+        <v>627</v>
+      </c>
+      <c r="L56" s="16" t="s">
+        <v>628</v>
+      </c>
+      <c r="M56" s="9" t="s">
+        <v>629</v>
+      </c>
+      <c r="N56" s="16" t="s">
+        <v>630</v>
+      </c>
+      <c r="O56" s="16" t="s">
+        <v>631</v>
+      </c>
+      <c r="P56" s="9" t="s">
+        <v>632</v>
+      </c>
+      <c r="Q56" s="16" t="s">
+        <v>633</v>
+      </c>
     </row>
-    <row r="57" spans="6:6">
-      <c r="F57" s="20"/>
+    <row r="57" ht="47" customHeight="1" spans="1:17">
+      <c r="A57" s="9" t="s">
+        <v>634</v>
+      </c>
+      <c r="B57" s="16" t="s">
+        <v>635</v>
+      </c>
+      <c r="C57" s="9" t="s">
+        <v>548</v>
+      </c>
+      <c r="D57" s="13"/>
+      <c r="E57" s="18">
+        <v>54860</v>
+      </c>
+      <c r="F57" s="14"/>
+      <c r="G57" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="H57" s="13"/>
+      <c r="I57" s="9" t="s">
+        <v>636</v>
+      </c>
+      <c r="J57" s="13"/>
+      <c r="K57" s="9" t="s">
+        <v>637</v>
+      </c>
+      <c r="L57" s="16" t="s">
+        <v>638</v>
+      </c>
+      <c r="M57" s="9" t="s">
+        <v>639</v>
+      </c>
+      <c r="N57" s="16" t="s">
+        <v>640</v>
+      </c>
+      <c r="O57" s="16" t="s">
+        <v>641</v>
+      </c>
+      <c r="P57" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="Q57" s="16" t="s">
+        <v>643</v>
+      </c>
     </row>
-    <row r="58" spans="6:6">
-      <c r="F58" s="20"/>
+    <row r="58" ht="47" customHeight="1" spans="1:17">
+      <c r="A58" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="B58" s="16" t="s">
+        <v>645</v>
+      </c>
+      <c r="C58" s="9" t="s">
+        <v>548</v>
+      </c>
+      <c r="D58" s="13"/>
+      <c r="E58" s="18">
+        <v>54861</v>
+      </c>
+      <c r="F58" s="14"/>
+      <c r="G58" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H58" s="13"/>
+      <c r="I58" s="9" t="s">
+        <v>646</v>
+      </c>
+      <c r="J58" s="13"/>
+      <c r="K58" s="9" t="s">
+        <v>647</v>
+      </c>
+      <c r="L58" s="16" t="s">
+        <v>648</v>
+      </c>
+      <c r="M58" s="9" t="s">
+        <v>649</v>
+      </c>
+      <c r="N58" s="16" t="s">
+        <v>650</v>
+      </c>
+      <c r="O58" s="16" t="s">
+        <v>651</v>
+      </c>
+      <c r="P58" s="9" t="s">
+        <v>652</v>
+      </c>
+      <c r="Q58" s="16" t="s">
+        <v>653</v>
+      </c>
     </row>
-    <row r="59" spans="6:6">
-      <c r="F59" s="20"/>
+    <row r="59" ht="47" customHeight="1" spans="1:17">
+      <c r="A59" s="9" t="s">
+        <v>654</v>
+      </c>
+      <c r="B59" s="16" t="s">
+        <v>655</v>
+      </c>
+      <c r="C59" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="D59" s="13"/>
+      <c r="E59" s="18">
+        <v>54852</v>
+      </c>
+      <c r="F59" s="14" t="s">
+        <v>656</v>
+      </c>
+      <c r="G59" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H59" s="13"/>
+      <c r="I59" s="9" t="s">
+        <v>657</v>
+      </c>
+      <c r="J59" s="13"/>
+      <c r="K59" s="9" t="s">
+        <v>658</v>
+      </c>
+      <c r="L59" s="16" t="s">
+        <v>659</v>
+      </c>
+      <c r="M59" s="9" t="s">
+        <v>660</v>
+      </c>
+      <c r="N59" s="16" t="s">
+        <v>661</v>
+      </c>
+      <c r="O59" s="16" t="s">
+        <v>662</v>
+      </c>
+      <c r="P59" s="9" t="s">
+        <v>663</v>
+      </c>
+      <c r="Q59" s="16" t="s">
+        <v>664</v>
+      </c>
     </row>
-    <row r="60" spans="6:6">
-      <c r="F60" s="20"/>
+    <row r="60" ht="47" customHeight="1" spans="1:17">
+      <c r="A60" s="9" t="s">
+        <v>665</v>
+      </c>
+      <c r="B60" s="16" t="s">
+        <v>666</v>
+      </c>
+      <c r="C60" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="D60" s="13"/>
+      <c r="E60" s="18">
+        <v>54851</v>
+      </c>
+      <c r="F60" s="14"/>
+      <c r="G60" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="H60" s="13"/>
+      <c r="I60" s="9" t="s">
+        <v>667</v>
+      </c>
+      <c r="J60" s="13"/>
+      <c r="K60" s="9" t="s">
+        <v>668</v>
+      </c>
+      <c r="L60" s="16" t="s">
+        <v>669</v>
+      </c>
+      <c r="M60" s="9" t="s">
+        <v>670</v>
+      </c>
+      <c r="N60" s="16" t="s">
+        <v>671</v>
+      </c>
+      <c r="O60" s="16" t="s">
+        <v>672</v>
+      </c>
+      <c r="P60" s="9" t="s">
+        <v>673</v>
+      </c>
+      <c r="Q60" s="16" t="s">
+        <v>674</v>
+      </c>
     </row>
-    <row r="61" spans="6:6">
-      <c r="F61" s="20"/>
+    <row r="61" ht="47" customHeight="1" spans="1:17">
+      <c r="A61" s="9" t="s">
+        <v>675</v>
+      </c>
+      <c r="B61" s="16" t="s">
+        <v>676</v>
+      </c>
+      <c r="C61" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="D61" s="13"/>
+      <c r="E61" s="18">
+        <v>54854</v>
+      </c>
+      <c r="F61" s="14"/>
+      <c r="G61" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H61" s="13"/>
+      <c r="I61" s="9" t="s">
+        <v>677</v>
+      </c>
+      <c r="J61" s="13"/>
+      <c r="K61" s="9" t="s">
+        <v>678</v>
+      </c>
+      <c r="L61" s="16" t="s">
+        <v>679</v>
+      </c>
+      <c r="M61" s="9" t="s">
+        <v>680</v>
+      </c>
+      <c r="N61" s="16" t="s">
+        <v>681</v>
+      </c>
+      <c r="O61" s="16" t="s">
+        <v>682</v>
+      </c>
+      <c r="P61" s="9" t="s">
+        <v>683</v>
+      </c>
+      <c r="Q61" s="16" t="s">
+        <v>684</v>
+      </c>
     </row>
-    <row r="62" spans="6:6">
-      <c r="F62" s="20"/>
+    <row r="62" ht="63.5" customHeight="1" spans="1:17">
+      <c r="A62" s="9" t="s">
+        <v>685</v>
+      </c>
+      <c r="B62" s="16" t="s">
+        <v>686</v>
+      </c>
+      <c r="C62" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="D62" s="13"/>
+      <c r="E62" s="18">
+        <v>54846</v>
+      </c>
+      <c r="F62" s="14"/>
+      <c r="G62" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="H62" s="13"/>
+      <c r="I62" s="9" t="s">
+        <v>687</v>
+      </c>
+      <c r="J62" s="13"/>
+      <c r="K62" s="9" t="s">
+        <v>688</v>
+      </c>
+      <c r="L62" s="16" t="s">
+        <v>689</v>
+      </c>
+      <c r="M62" s="9" t="s">
+        <v>690</v>
+      </c>
+      <c r="N62" s="16" t="s">
+        <v>691</v>
+      </c>
+      <c r="O62" s="16" t="s">
+        <v>692</v>
+      </c>
+      <c r="P62" s="9" t="s">
+        <v>693</v>
+      </c>
+      <c r="Q62" s="16" t="s">
+        <v>694</v>
+      </c>
     </row>
-    <row r="63" spans="6:6">
-      <c r="F63" s="20"/>
-    </row>
-    <row r="64" spans="6:6">
-      <c r="F64" s="20"/>
-    </row>
-    <row r="65" spans="6:18">
-      <c r="F65" s="20"/>
-    </row>
-    <row r="66" spans="6:18">
-      <c r="F66" s="20"/>
-    </row>
+    <row r="66" ht="15"/>
     <row r="67" spans="6:18">
-      <c r="F67" s="20"/>
+      <c r="F67" s="21"/>
+      <c r="G67" s="21"/>
+      <c r="H67" s="21"/>
+      <c r="I67" s="22"/>
+      <c r="J67" s="21"/>
+      <c r="K67" s="22"/>
+      <c r="L67" s="21"/>
+      <c r="M67" s="23"/>
     </row>
     <row r="68" spans="6:18">
       <c r="F68" s="21"/>
@@ -9425,14 +10822,14 @@
       <c r="M70" s="23"/>
     </row>
     <row r="71" spans="6:18">
-      <c r="F71" s="21"/>
-      <c r="G71" s="21"/>
-      <c r="H71" s="21"/>
-      <c r="I71" s="22"/>
-      <c r="J71" s="21"/>
-      <c r="K71" s="22"/>
-      <c r="L71" s="21"/>
-      <c r="M71" s="23"/>
+      <c r="F71" s="24"/>
+      <c r="G71" s="24"/>
+      <c r="H71" s="24"/>
+      <c r="I71" s="25"/>
+      <c r="J71" s="24"/>
+      <c r="K71" s="25"/>
+      <c r="L71" s="24"/>
+      <c r="M71" s="26"/>
     </row>
     <row r="72" spans="6:18">
       <c r="F72" s="24"/>
@@ -9442,33 +10839,34 @@
       <c r="J72" s="24"/>
       <c r="K72" s="25"/>
       <c r="L72" s="24"/>
-      <c r="M72" s="26"/>
+      <c r="M72" s="27"/>
     </row>
     <row r="73" spans="6:18">
-      <c r="F73" s="24"/>
-      <c r="G73" s="24"/>
-      <c r="H73" s="24"/>
-      <c r="I73" s="25"/>
-      <c r="J73" s="24"/>
-      <c r="K73" s="25"/>
-      <c r="L73" s="24"/>
-      <c r="M73" s="27"/>
+      <c r="F73" s="21"/>
+      <c r="G73" s="26"/>
+      <c r="H73" s="26"/>
+      <c r="I73" s="26"/>
+      <c r="J73" s="26"/>
+      <c r="K73" s="26"/>
+      <c r="L73" s="26"/>
+      <c r="M73" s="26"/>
     </row>
-    <row r="74" spans="6:18">
-      <c r="F74" s="21"/>
-      <c r="G74" s="26"/>
-      <c r="H74" s="26"/>
-      <c r="I74" s="26"/>
-      <c r="J74" s="26"/>
-      <c r="K74" s="26"/>
-      <c r="L74" s="26"/>
-      <c r="M74" s="26"/>
+    <row r="74" ht="13.5" spans="6:18">
+      <c r="F74" s="28"/>
     </row>
-    <row r="75" ht="13.5" spans="6:18">
-      <c r="F75" s="20"/>
+    <row r="75" ht="16.5" spans="6:18">
+      <c r="F75" s="28"/>
+      <c r="K75" s="5"/>
+      <c r="L75" s="5"/>
+      <c r="M75" s="5"/>
+      <c r="N75" s="5"/>
+      <c r="O75" s="8"/>
+      <c r="P75" s="5"/>
+      <c r="Q75"/>
+      <c r="R75" s="6"/>
     </row>
     <row r="76" ht="16.5" spans="6:18">
-      <c r="F76" s="20"/>
+      <c r="F76" s="28"/>
       <c r="K76" s="5"/>
       <c r="L76" s="5"/>
       <c r="M76" s="5"/>
@@ -9479,7 +10877,6 @@
       <c r="R76" s="6"/>
     </row>
     <row r="77" ht="16.5" spans="6:18">
-      <c r="F77" s="20"/>
       <c r="K77" s="5"/>
       <c r="L77" s="5"/>
       <c r="M77" s="5"/>
@@ -9511,7 +10908,7 @@
     </row>
     <row r="80" ht="16.5" spans="6:18">
       <c r="K80" s="5"/>
-      <c r="L80" s="5"/>
+      <c r="L80" s="10"/>
       <c r="M80" s="5"/>
       <c r="N80" s="5"/>
       <c r="O80" s="8"/>
@@ -9521,7 +10918,7 @@
     </row>
     <row r="81" ht="16.5" spans="11:18">
       <c r="K81" s="5"/>
-      <c r="L81" s="9"/>
+      <c r="L81" s="5"/>
       <c r="M81" s="5"/>
       <c r="N81" s="5"/>
       <c r="O81" s="8"/>
@@ -9610,144 +11007,134 @@
       <c r="R89" s="6"/>
     </row>
     <row r="90" ht="16.5" spans="11:18">
-      <c r="K90" s="5"/>
-      <c r="L90" s="5"/>
-      <c r="M90" s="5"/>
+      <c r="K90" s="29"/>
+      <c r="L90" s="29"/>
+      <c r="M90" s="29"/>
       <c r="N90" s="5"/>
       <c r="O90" s="8"/>
-      <c r="P90" s="5"/>
+      <c r="P90" s="29"/>
       <c r="Q90"/>
-      <c r="R90" s="6"/>
+      <c r="R90" s="30"/>
     </row>
     <row r="91" ht="16.5" spans="11:18">
-      <c r="K91" s="10"/>
-      <c r="L91" s="10"/>
-      <c r="M91" s="10"/>
+      <c r="K91" s="29"/>
+      <c r="L91" s="29"/>
+      <c r="M91" s="29"/>
       <c r="N91" s="5"/>
       <c r="O91" s="8"/>
-      <c r="P91" s="10"/>
+      <c r="P91" s="29"/>
       <c r="Q91"/>
-      <c r="R91" s="28"/>
+      <c r="R91" s="31"/>
     </row>
     <row r="92" ht="16.5" spans="11:18">
-      <c r="K92" s="10"/>
-      <c r="L92" s="10"/>
-      <c r="M92" s="10"/>
+      <c r="K92" s="29"/>
+      <c r="L92" s="29"/>
+      <c r="M92" s="29"/>
       <c r="N92" s="5"/>
       <c r="O92" s="8"/>
-      <c r="P92" s="10"/>
+      <c r="P92" s="29"/>
       <c r="Q92"/>
-      <c r="R92" s="12"/>
+      <c r="R92" s="30"/>
     </row>
     <row r="93" ht="16.5" spans="11:18">
-      <c r="K93" s="10"/>
-      <c r="L93" s="10"/>
-      <c r="M93" s="10"/>
+      <c r="K93" s="29"/>
+      <c r="L93" s="29"/>
+      <c r="M93" s="29"/>
       <c r="N93" s="5"/>
       <c r="O93" s="8"/>
-      <c r="P93" s="10"/>
+      <c r="P93" s="29"/>
       <c r="Q93"/>
-      <c r="R93" s="28"/>
+      <c r="R93" s="31"/>
     </row>
     <row r="94" ht="16.5" spans="11:18">
-      <c r="K94" s="10"/>
-      <c r="L94" s="10"/>
-      <c r="M94" s="10"/>
+      <c r="K94" s="29"/>
+      <c r="L94" s="29"/>
+      <c r="M94" s="29"/>
       <c r="N94" s="5"/>
       <c r="O94" s="8"/>
-      <c r="P94" s="10"/>
+      <c r="P94" s="29"/>
       <c r="Q94"/>
-      <c r="R94" s="12"/>
+      <c r="R94" s="31"/>
     </row>
     <row r="95" ht="16.5" spans="11:18">
-      <c r="K95" s="10"/>
-      <c r="L95" s="10"/>
-      <c r="M95" s="10"/>
+      <c r="K95" s="29"/>
+      <c r="L95" s="29"/>
+      <c r="M95" s="29"/>
       <c r="N95" s="5"/>
       <c r="O95" s="8"/>
-      <c r="P95" s="10"/>
+      <c r="P95" s="29"/>
       <c r="Q95"/>
-      <c r="R95" s="12"/>
+      <c r="R95" s="31"/>
     </row>
     <row r="96" ht="16.5" spans="11:18">
-      <c r="K96" s="10"/>
-      <c r="L96" s="10"/>
-      <c r="M96" s="10"/>
+      <c r="K96" s="29"/>
+      <c r="L96" s="29"/>
+      <c r="M96" s="29"/>
       <c r="N96" s="5"/>
       <c r="O96" s="8"/>
-      <c r="P96" s="10"/>
-      <c r="Q96"/>
-      <c r="R96" s="12"/>
+      <c r="R96" s="31"/>
     </row>
     <row r="97" ht="16.5" spans="11:18">
-      <c r="K97" s="10"/>
-      <c r="L97" s="10"/>
-      <c r="M97" s="10"/>
+      <c r="K97" s="29"/>
+      <c r="L97" s="29"/>
+      <c r="M97" s="29"/>
       <c r="N97" s="5"/>
-      <c r="O97" s="8"/>
-      <c r="R97" s="12"/>
+      <c r="O97" s="29"/>
+      <c r="P97" s="29"/>
+      <c r="R97" s="31"/>
     </row>
     <row r="98" ht="16.5" spans="11:18">
-      <c r="K98" s="10"/>
-      <c r="L98" s="10"/>
-      <c r="M98" s="10"/>
+      <c r="K98" s="29"/>
+      <c r="L98" s="29"/>
+      <c r="M98" s="29"/>
       <c r="N98" s="5"/>
-      <c r="O98" s="10"/>
-      <c r="P98" s="10"/>
-      <c r="R98" s="12"/>
+      <c r="R98" s="31"/>
     </row>
     <row r="99" ht="16.5" spans="11:18">
-      <c r="K99" s="10"/>
-      <c r="L99" s="10"/>
-      <c r="M99" s="10"/>
+      <c r="K99" s="29"/>
+      <c r="L99" s="29"/>
+      <c r="M99" s="29"/>
       <c r="N99" s="5"/>
-      <c r="R99" s="12"/>
+      <c r="R99" s="31"/>
     </row>
     <row r="100" ht="16.5" spans="11:18">
-      <c r="K100" s="10"/>
-      <c r="L100" s="10"/>
-      <c r="M100" s="10"/>
-      <c r="N100" s="5"/>
-      <c r="R100" s="12"/>
+      <c r="K100" s="5"/>
+      <c r="L100" s="5"/>
     </row>
     <row r="101" ht="16.5" spans="11:18">
       <c r="K101" s="5"/>
       <c r="L101" s="5"/>
-    </row>
-    <row r="102" ht="16.5" spans="11:18">
-      <c r="K102" s="5"/>
-      <c r="L102" s="5"/>
-      <c r="M102" s="10"/>
-      <c r="N102" s="5"/>
-      <c r="R102" s="12"/>
+      <c r="M101" s="29"/>
+      <c r="N101" s="5"/>
+      <c r="R101" s="31"/>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="H1:H77" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="H1:H76" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <hyperlinks>
-    <hyperlink ref="J2" r:id="rId98" display="170.101.101.188" tooltip="http://170.101.101.188"/>
-    <hyperlink ref="J3" r:id="rId98" display="170.101.101.188" tooltip="http://170.101.101.188"/>
-    <hyperlink ref="J4" r:id="rId98" display="170.101.101.188" tooltip="http://170.101.101.188"/>
-    <hyperlink ref="J5" r:id="rId98" display="170.101.101.188" tooltip="http://170.101.101.188"/>
-    <hyperlink ref="J6" r:id="rId98" display="170.101.101.188" tooltip="http://170.101.101.188"/>
-    <hyperlink ref="J7" r:id="rId98" display="170.101.101.188" tooltip="http://170.101.101.188"/>
-    <hyperlink ref="J8" r:id="rId98" display="170.101.101.188" tooltip="http://170.101.101.188"/>
-    <hyperlink ref="J9" r:id="rId98" display="170.101.101.188" tooltip="http://170.101.101.188"/>
-    <hyperlink ref="J10" r:id="rId98" display="170.101.101.188" tooltip="http://170.101.101.188"/>
-    <hyperlink ref="J11" r:id="rId98" display="170.101.101.188" tooltip="http://170.101.101.188"/>
-    <hyperlink ref="J12" r:id="rId98" display="170.101.101.188" tooltip="http://170.101.101.188"/>
-    <hyperlink ref="J13" r:id="rId98" display="170.101.101.188" tooltip="http://170.101.101.188"/>
-    <hyperlink ref="J14" r:id="rId98" display="170.101.101.188" tooltip="http://170.101.101.188"/>
-    <hyperlink ref="J15" r:id="rId98" display="170.101.101.188" tooltip="http://170.101.101.188"/>
-    <hyperlink ref="J16" r:id="rId98" display="170.101.101.188" tooltip="http://170.101.101.188"/>
-    <hyperlink ref="J17" r:id="rId98" display="170.101.101.188" tooltip="http://170.101.101.188"/>
-    <hyperlink ref="J18" r:id="rId98" display="170.101.101.188" tooltip="http://170.101.101.188"/>
-    <hyperlink ref="J19" r:id="rId98" display="170.101.101.188" tooltip="http://170.101.101.188"/>
-    <hyperlink ref="J20" r:id="rId98" display="170.101.101.188" tooltip="http://170.101.101.188"/>
-    <hyperlink ref="J21" r:id="rId98" display="170.101.101.188" tooltip="http://170.101.101.188"/>
-    <hyperlink ref="J22" r:id="rId98" display="170.101.101.188" tooltip="http://170.101.101.188"/>
-    <hyperlink ref="J27" r:id="rId98" display="170.101.101.188" tooltip="http://170.101.101.188"/>
+    <hyperlink ref="J2" r:id="rId97" display="170.101.101.188" tooltip="http://170.101.101.188"/>
+    <hyperlink ref="J3" r:id="rId97" display="170.101.101.188" tooltip="http://170.101.101.188"/>
+    <hyperlink ref="J4" r:id="rId97" display="170.101.101.188" tooltip="http://170.101.101.188"/>
+    <hyperlink ref="J5" r:id="rId97" display="170.101.101.188" tooltip="http://170.101.101.188"/>
+    <hyperlink ref="J6" r:id="rId97" display="170.101.101.188" tooltip="http://170.101.101.188"/>
+    <hyperlink ref="J7" r:id="rId97" display="170.101.101.188" tooltip="http://170.101.101.188"/>
+    <hyperlink ref="J8" r:id="rId97" display="170.101.101.188" tooltip="http://170.101.101.188"/>
+    <hyperlink ref="J9" r:id="rId97" display="170.101.101.188" tooltip="http://170.101.101.188"/>
+    <hyperlink ref="J10" r:id="rId97" display="170.101.101.188" tooltip="http://170.101.101.188"/>
+    <hyperlink ref="J11" r:id="rId97" display="170.101.101.188" tooltip="http://170.101.101.188"/>
+    <hyperlink ref="J12" r:id="rId97" display="170.101.101.188" tooltip="http://170.101.101.188"/>
+    <hyperlink ref="J13" r:id="rId97" display="170.101.101.188" tooltip="http://170.101.101.188"/>
+    <hyperlink ref="J14" r:id="rId97" display="170.101.101.188" tooltip="http://170.101.101.188"/>
+    <hyperlink ref="J15" r:id="rId97" display="170.101.101.188" tooltip="http://170.101.101.188"/>
+    <hyperlink ref="J16" r:id="rId97" display="170.101.101.188" tooltip="http://170.101.101.188"/>
+    <hyperlink ref="J17" r:id="rId97" display="170.101.101.188" tooltip="http://170.101.101.188"/>
+    <hyperlink ref="J18" r:id="rId97" display="170.101.101.188" tooltip="http://170.101.101.188"/>
+    <hyperlink ref="J19" r:id="rId97" display="170.101.101.188" tooltip="http://170.101.101.188"/>
+    <hyperlink ref="J20" r:id="rId97" display="170.101.101.188" tooltip="http://170.101.101.188"/>
+    <hyperlink ref="J21" r:id="rId97" display="170.101.101.188" tooltip="http://170.101.101.188"/>
+    <hyperlink ref="J22" r:id="rId97" display="170.101.101.188" tooltip="http://170.101.101.188"/>
+    <hyperlink ref="J27" r:id="rId97" display="170.101.101.188" tooltip="http://170.101.101.188"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -11643,8 +13030,8 @@
               <to>
                 <xdr:col>4</xdr:col>
                 <xdr:colOff>1143635</xdr:colOff>
-                <xdr:row>47</xdr:row>
-                <xdr:rowOff>9525</xdr:rowOff>
+                <xdr:row>46</xdr:row>
+                <xdr:rowOff>180975</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
@@ -11668,8 +13055,8 @@
               <to>
                 <xdr:col>4</xdr:col>
                 <xdr:colOff>1143635</xdr:colOff>
-                <xdr:row>48</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
+                <xdr:row>47</xdr:row>
+                <xdr:rowOff>180975</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
@@ -11687,14 +13074,14 @@
               <from>
                 <xdr:col>4</xdr:col>
                 <xdr:colOff>0</xdr:colOff>
-                <xdr:row>48</xdr:row>
+                <xdr:row>58</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>4</xdr:col>
                 <xdr:colOff>1143635</xdr:colOff>
-                <xdr:row>49</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
+                <xdr:row>58</xdr:row>
+                <xdr:rowOff>180975</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
@@ -11712,14 +13099,14 @@
               <from>
                 <xdr:col>4</xdr:col>
                 <xdr:colOff>0</xdr:colOff>
-                <xdr:row>49</xdr:row>
+                <xdr:row>59</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>4</xdr:col>
                 <xdr:colOff>1143635</xdr:colOff>
-                <xdr:row>50</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
+                <xdr:row>59</xdr:row>
+                <xdr:rowOff>180975</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
@@ -11737,14 +13124,14 @@
               <from>
                 <xdr:col>4</xdr:col>
                 <xdr:colOff>0</xdr:colOff>
-                <xdr:row>50</xdr:row>
+                <xdr:row>60</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>4</xdr:col>
                 <xdr:colOff>1143635</xdr:colOff>
-                <xdr:row>51</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
+                <xdr:row>60</xdr:row>
+                <xdr:rowOff>180975</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
@@ -11762,14 +13149,14 @@
               <from>
                 <xdr:col>4</xdr:col>
                 <xdr:colOff>0</xdr:colOff>
-                <xdr:row>53</xdr:row>
+                <xdr:row>48</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>4</xdr:col>
                 <xdr:colOff>1143635</xdr:colOff>
-                <xdr:row>54</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
+                <xdr:row>48</xdr:row>
+                <xdr:rowOff>180975</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
@@ -11787,14 +13174,14 @@
               <from>
                 <xdr:col>4</xdr:col>
                 <xdr:colOff>0</xdr:colOff>
-                <xdr:row>54</xdr:row>
+                <xdr:row>49</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>4</xdr:col>
                 <xdr:colOff>1143635</xdr:colOff>
-                <xdr:row>55</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
+                <xdr:row>49</xdr:row>
+                <xdr:rowOff>180975</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
@@ -11812,14 +13199,14 @@
               <from>
                 <xdr:col>4</xdr:col>
                 <xdr:colOff>0</xdr:colOff>
-                <xdr:row>55</xdr:row>
+                <xdr:row>50</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>4</xdr:col>
                 <xdr:colOff>1143635</xdr:colOff>
-                <xdr:row>56</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
+                <xdr:row>50</xdr:row>
+                <xdr:rowOff>180975</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
@@ -11837,14 +13224,14 @@
               <from>
                 <xdr:col>4</xdr:col>
                 <xdr:colOff>0</xdr:colOff>
-                <xdr:row>56</xdr:row>
+                <xdr:row>51</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>4</xdr:col>
                 <xdr:colOff>1143635</xdr:colOff>
-                <xdr:row>57</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
+                <xdr:row>51</xdr:row>
+                <xdr:rowOff>180975</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
@@ -11862,14 +13249,14 @@
               <from>
                 <xdr:col>4</xdr:col>
                 <xdr:colOff>0</xdr:colOff>
-                <xdr:row>57</xdr:row>
+                <xdr:row>52</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>4</xdr:col>
                 <xdr:colOff>1143635</xdr:colOff>
-                <xdr:row>58</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
+                <xdr:row>52</xdr:row>
+                <xdr:rowOff>180975</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
@@ -11887,14 +13274,14 @@
               <from>
                 <xdr:col>4</xdr:col>
                 <xdr:colOff>0</xdr:colOff>
-                <xdr:row>58</xdr:row>
+                <xdr:row>53</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>4</xdr:col>
                 <xdr:colOff>1143635</xdr:colOff>
-                <xdr:row>59</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
+                <xdr:row>53</xdr:row>
+                <xdr:rowOff>180975</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
@@ -11912,14 +13299,14 @@
               <from>
                 <xdr:col>4</xdr:col>
                 <xdr:colOff>0</xdr:colOff>
-                <xdr:row>59</xdr:row>
+                <xdr:row>54</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>4</xdr:col>
                 <xdr:colOff>1143635</xdr:colOff>
-                <xdr:row>60</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
+                <xdr:row>54</xdr:row>
+                <xdr:rowOff>180975</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
@@ -11937,14 +13324,14 @@
               <from>
                 <xdr:col>4</xdr:col>
                 <xdr:colOff>0</xdr:colOff>
-                <xdr:row>60</xdr:row>
+                <xdr:row>55</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>4</xdr:col>
                 <xdr:colOff>1143635</xdr:colOff>
-                <xdr:row>61</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
+                <xdr:row>55</xdr:row>
+                <xdr:rowOff>180975</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
@@ -11962,14 +13349,14 @@
               <from>
                 <xdr:col>4</xdr:col>
                 <xdr:colOff>0</xdr:colOff>
-                <xdr:row>61</xdr:row>
+                <xdr:row>56</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>4</xdr:col>
                 <xdr:colOff>1143635</xdr:colOff>
-                <xdr:row>62</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
+                <xdr:row>56</xdr:row>
+                <xdr:rowOff>180975</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
@@ -11987,14 +13374,14 @@
               <from>
                 <xdr:col>4</xdr:col>
                 <xdr:colOff>0</xdr:colOff>
-                <xdr:row>62</xdr:row>
+                <xdr:row>57</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>4</xdr:col>
                 <xdr:colOff>1143635</xdr:colOff>
-                <xdr:row>63</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
+                <xdr:row>57</xdr:row>
+                <xdr:rowOff>180975</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
@@ -12006,19 +13393,19 @@
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="1115" r:id="rId93">
+        <control shapeId="1116" r:id="rId93">
           <controlPr defaultSize="0">
             <anchor moveWithCells="1">
               <from>
-                <xdr:col>4</xdr:col>
+                <xdr:col>5</xdr:col>
                 <xdr:colOff>0</xdr:colOff>
-                <xdr:row>63</xdr:row>
+                <xdr:row>67</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
-                <xdr:col>4</xdr:col>
-                <xdr:colOff>1143635</xdr:colOff>
-                <xdr:row>64</xdr:row>
+                <xdr:col>5</xdr:col>
+                <xdr:colOff>1448435</xdr:colOff>
+                <xdr:row>68</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </to>
             </anchor>
@@ -12026,12 +13413,12 @@
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="1115" r:id="rId93"/>
+        <control shapeId="1116" r:id="rId93"/>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="1116" r:id="rId94">
+        <control shapeId="1117" r:id="rId94">
           <controlPr defaultSize="0">
             <anchor moveWithCells="1">
               <from>
@@ -12051,12 +13438,12 @@
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="1116" r:id="rId94"/>
+        <control shapeId="1117" r:id="rId94"/>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="1117" r:id="rId95">
+        <control shapeId="1118" r:id="rId95">
           <controlPr defaultSize="0">
             <anchor moveWithCells="1">
               <from>
@@ -12076,12 +13463,12 @@
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="1117" r:id="rId95"/>
+        <control shapeId="1118" r:id="rId95"/>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="1118" r:id="rId96">
+        <control shapeId="1119" r:id="rId96">
           <controlPr defaultSize="0">
             <anchor moveWithCells="1">
               <from>
@@ -12101,32 +13488,7 @@
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="1118" r:id="rId96"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="1119" r:id="rId97">
-          <controlPr defaultSize="0">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>5</xdr:col>
-                <xdr:colOff>0</xdr:colOff>
-                <xdr:row>71</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>5</xdr:col>
-                <xdr:colOff>1448435</xdr:colOff>
-                <xdr:row>72</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="1119" r:id="rId97"/>
+        <control shapeId="1119" r:id="rId96"/>
       </mc:Fallback>
     </mc:AlternateContent>
   </controls>
